--- a/clean/chemistry/chem_heavy_metals_2024.xlsx
+++ b/clean/chemistry/chem_heavy_metals_2024.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$DX$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$CZ$221</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DX221"/>
+  <dimension ref="A1:CZ221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -543,35 +543,11 @@
     <col width="20" customWidth="1" min="97" max="97"/>
     <col width="24" customWidth="1" min="98" max="98"/>
     <col width="22" customWidth="1" min="99" max="99"/>
-    <col width="16" customWidth="1" min="100" max="100"/>
-    <col width="12" customWidth="1" min="101" max="101"/>
-    <col width="12" customWidth="1" min="102" max="102"/>
-    <col width="13" customWidth="1" min="103" max="103"/>
-    <col width="12" customWidth="1" min="104" max="104"/>
-    <col width="12" customWidth="1" min="105" max="105"/>
-    <col width="14" customWidth="1" min="106" max="106"/>
-    <col width="12" customWidth="1" min="107" max="107"/>
-    <col width="12" customWidth="1" min="108" max="108"/>
-    <col width="13" customWidth="1" min="109" max="109"/>
-    <col width="12" customWidth="1" min="110" max="110"/>
-    <col width="12" customWidth="1" min="111" max="111"/>
-    <col width="12" customWidth="1" min="112" max="112"/>
-    <col width="14" customWidth="1" min="113" max="113"/>
-    <col width="12" customWidth="1" min="114" max="114"/>
-    <col width="12" customWidth="1" min="115" max="115"/>
-    <col width="13" customWidth="1" min="116" max="116"/>
-    <col width="13" customWidth="1" min="117" max="117"/>
-    <col width="14" customWidth="1" min="118" max="118"/>
-    <col width="12" customWidth="1" min="119" max="119"/>
-    <col width="12" customWidth="1" min="120" max="120"/>
-    <col width="13" customWidth="1" min="121" max="121"/>
-    <col width="12" customWidth="1" min="122" max="122"/>
-    <col width="12" customWidth="1" min="123" max="123"/>
-    <col width="14" customWidth="1" min="124" max="124"/>
-    <col width="14" customWidth="1" min="125" max="125"/>
-    <col width="12" customWidth="1" min="126" max="126"/>
-    <col width="24" customWidth="1" min="127" max="127"/>
-    <col width="10" customWidth="1" min="128" max="128"/>
+    <col width="17" customWidth="1" min="100" max="100"/>
+    <col width="28" customWidth="1" min="101" max="101"/>
+    <col width="15" customWidth="1" min="102" max="102"/>
+    <col width="33" customWidth="1" min="103" max="103"/>
+    <col width="13" customWidth="1" min="104" max="104"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1072,147 +1048,27 @@
       </c>
       <c r="CV1" s="1" t="inlineStr">
         <is>
-          <t>qc_for_invalid</t>
+          <t>validity_status</t>
         </is>
       </c>
       <c r="CW1" s="1" t="inlineStr">
         <is>
-          <t>qc_result</t>
+          <t>sample_category_canonical</t>
         </is>
       </c>
       <c r="CX1" s="1" t="inlineStr">
         <is>
-          <t>silver_qc</t>
+          <t>category_flag</t>
         </is>
       </c>
       <c r="CY1" s="1" t="inlineStr">
         <is>
-          <t>aluminum_qc</t>
+          <t>sample_name_group</t>
         </is>
       </c>
       <c r="CZ1" s="1" t="inlineStr">
         <is>
-          <t>arsenic_qc</t>
-        </is>
-      </c>
-      <c r="DA1" s="1" t="inlineStr">
-        <is>
-          <t>barium_qc</t>
-        </is>
-      </c>
-      <c r="DB1" s="1" t="inlineStr">
-        <is>
-          <t>beryllium_qc</t>
-        </is>
-      </c>
-      <c r="DC1" s="1" t="inlineStr">
-        <is>
-          <t>cadmium_qc</t>
-        </is>
-      </c>
-      <c r="DD1" s="1" t="inlineStr">
-        <is>
-          <t>cobalt_qc</t>
-        </is>
-      </c>
-      <c r="DE1" s="1" t="inlineStr">
-        <is>
-          <t>chromium_qc</t>
-        </is>
-      </c>
-      <c r="DF1" s="1" t="inlineStr">
-        <is>
-          <t>cesium_qc</t>
-        </is>
-      </c>
-      <c r="DG1" s="1" t="inlineStr">
-        <is>
-          <t>copper_qc</t>
-        </is>
-      </c>
-      <c r="DH1" s="1" t="inlineStr">
-        <is>
-          <t>iron_qc</t>
-        </is>
-      </c>
-      <c r="DI1" s="1" t="inlineStr">
-        <is>
-          <t>manganese_qc</t>
-        </is>
-      </c>
-      <c r="DJ1" s="1" t="inlineStr">
-        <is>
-          <t>nickel_qc</t>
-        </is>
-      </c>
-      <c r="DK1" s="1" t="inlineStr">
-        <is>
-          <t>lead_qc</t>
-        </is>
-      </c>
-      <c r="DL1" s="1" t="inlineStr">
-        <is>
-          <t>rubidium_qc</t>
-        </is>
-      </c>
-      <c r="DM1" s="1" t="inlineStr">
-        <is>
-          <t>selenium_qc</t>
-        </is>
-      </c>
-      <c r="DN1" s="1" t="inlineStr">
-        <is>
-          <t>strontium_qc</t>
-        </is>
-      </c>
-      <c r="DO1" s="1" t="inlineStr">
-        <is>
-          <t>uranium_qc</t>
-        </is>
-      </c>
-      <c r="DP1" s="1" t="inlineStr">
-        <is>
-          <t>mercury_qc</t>
-        </is>
-      </c>
-      <c r="DQ1" s="1" t="inlineStr">
-        <is>
-          <t>vanadium_qc</t>
-        </is>
-      </c>
-      <c r="DR1" s="1" t="inlineStr">
-        <is>
-          <t>zinc_qc</t>
-        </is>
-      </c>
-      <c r="DS1" s="1" t="inlineStr">
-        <is>
-          <t>calcium_qc</t>
-        </is>
-      </c>
-      <c r="DT1" s="1" t="inlineStr">
-        <is>
-          <t>potassium_qc</t>
-        </is>
-      </c>
-      <c r="DU1" s="1" t="inlineStr">
-        <is>
-          <t>magnesium_qc</t>
-        </is>
-      </c>
-      <c r="DV1" s="1" t="inlineStr">
-        <is>
-          <t>sodium_qc</t>
-        </is>
-      </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>municipality_canonical</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>sector</t>
+          <t>sample_code</t>
         </is>
       </c>
     </row>
@@ -1437,14 +1293,19 @@
       <c r="CT2" t="n">
         <v>0</v>
       </c>
-      <c r="DW2" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV2" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>سمك بلطي ني</t>
         </is>
       </c>
     </row>
@@ -1669,14 +1530,19 @@
       <c r="CT3" t="n">
         <v>0</v>
       </c>
-      <c r="DW3" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX3" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>سمك بوري ني</t>
         </is>
       </c>
     </row>
@@ -1917,14 +1783,19 @@
           <t>Arsenic</t>
         </is>
       </c>
-      <c r="DW4" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX4" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV4" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY4" t="inlineStr">
+        <is>
+          <t>جمبري وسط ني</t>
         </is>
       </c>
     </row>
@@ -2149,14 +2020,19 @@
       <c r="CT5" t="n">
         <v>0</v>
       </c>
-      <c r="DW5" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX5" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>سمك سلمون ني</t>
         </is>
       </c>
     </row>
@@ -2381,14 +2257,19 @@
       <c r="CT6" t="n">
         <v>0</v>
       </c>
-      <c r="DW6" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX6" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>سمك دنيس ني</t>
         </is>
       </c>
     </row>
@@ -2613,14 +2494,19 @@
       <c r="CT7" t="n">
         <v>0</v>
       </c>
-      <c r="DW7" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX7" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY7" t="inlineStr">
+        <is>
+          <t>سمك شعور ني</t>
         </is>
       </c>
     </row>
@@ -2845,14 +2731,19 @@
       <c r="CT8" t="n">
         <v>0</v>
       </c>
-      <c r="DW8" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX8" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>سمك كنعد ني</t>
         </is>
       </c>
     </row>
@@ -3077,14 +2968,19 @@
       <c r="CT9" t="n">
         <v>0</v>
       </c>
-      <c r="DW9" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX9" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>سمك دنيس ني</t>
         </is>
       </c>
     </row>
@@ -3309,14 +3205,19 @@
       <c r="CT10" t="n">
         <v>0</v>
       </c>
-      <c r="DW10" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX10" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV10" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW10" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY10" t="inlineStr">
+        <is>
+          <t>سمك بوري ني</t>
         </is>
       </c>
     </row>
@@ -3562,14 +3463,19 @@
       <c r="CT11" t="n">
         <v>0</v>
       </c>
-      <c r="DW11" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX11" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV11" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW11" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY11" t="inlineStr">
+        <is>
+          <t>مياة سخان</t>
         </is>
       </c>
     </row>
@@ -3815,14 +3721,19 @@
       <c r="CT12" t="n">
         <v>0</v>
       </c>
-      <c r="DW12" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX12" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV12" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW12" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY12" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -4068,14 +3979,19 @@
       <c r="CT13" t="n">
         <v>0</v>
       </c>
-      <c r="DW13" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX13" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV13" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW13" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY13" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -4316,14 +4232,19 @@
           <t>Lead</t>
         </is>
       </c>
-      <c r="DW14" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX14" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV14" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="CW14" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY14" t="inlineStr">
+        <is>
+          <t>جمبري وسط - مزارع</t>
         </is>
       </c>
     </row>
@@ -4564,14 +4485,19 @@
           <t>Cadmium|Lead|Zinc</t>
         </is>
       </c>
-      <c r="DW15" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX15" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV15" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="CW15" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY15" t="inlineStr">
+        <is>
+          <t>جمبري وسط - بحر</t>
         </is>
       </c>
     </row>
@@ -4796,14 +4722,19 @@
       <c r="CT16" t="n">
         <v>0</v>
       </c>
-      <c r="DW16" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX16" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV16" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW16" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY16" t="inlineStr">
+        <is>
+          <t>السمك بوري</t>
         </is>
       </c>
     </row>
@@ -5028,14 +4959,19 @@
       <c r="CT17" t="n">
         <v>0</v>
       </c>
-      <c r="DW17" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX17" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV17" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW17" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY17" t="inlineStr">
+        <is>
+          <t>سمك دنيس</t>
         </is>
       </c>
     </row>
@@ -5260,14 +5196,19 @@
       <c r="CT18" t="n">
         <v>0</v>
       </c>
-      <c r="DW18" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX18" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV18" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW18" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY18" t="inlineStr">
+        <is>
+          <t>سمك بلطي</t>
         </is>
       </c>
     </row>
@@ -5492,14 +5433,19 @@
       <c r="CT19" t="n">
         <v>0</v>
       </c>
-      <c r="DW19" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX19" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV19" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW19" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY19" t="inlineStr">
+        <is>
+          <t>سمك سلمون</t>
         </is>
       </c>
     </row>
@@ -5707,14 +5653,24 @@
       <c r="CT20" t="n">
         <v>0</v>
       </c>
-      <c r="DW20" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX20" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV20" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="CW20" t="inlineStr">
+        <is>
+          <t>أغذية متنوعة</t>
+        </is>
+      </c>
+      <c r="CX20" t="inlineStr">
+        <is>
+          <t>defaulted</t>
+        </is>
+      </c>
+      <c r="CY20" t="inlineStr">
+        <is>
+          <t>محار</t>
         </is>
       </c>
     </row>
@@ -5922,14 +5878,24 @@
       <c r="CT21" t="n">
         <v>0</v>
       </c>
-      <c r="DW21" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX21" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV21" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="CW21" t="inlineStr">
+        <is>
+          <t>أغذية متنوعة</t>
+        </is>
+      </c>
+      <c r="CX21" t="inlineStr">
+        <is>
+          <t>defaulted</t>
+        </is>
+      </c>
+      <c r="CY21" t="inlineStr">
+        <is>
+          <t>كابوريا</t>
         </is>
       </c>
     </row>
@@ -6154,14 +6120,19 @@
       <c r="CT22" t="n">
         <v>0</v>
       </c>
-      <c r="DW22" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX22" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV22" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW22" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY22" t="inlineStr">
+        <is>
+          <t>سمك اروص</t>
         </is>
       </c>
     </row>
@@ -6386,14 +6357,19 @@
       <c r="CT23" t="n">
         <v>0</v>
       </c>
-      <c r="DW23" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX23" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV23" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW23" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY23" t="inlineStr">
+        <is>
+          <t>سمك هامور</t>
         </is>
       </c>
     </row>
@@ -6618,14 +6594,19 @@
       <c r="CT24" t="n">
         <v>0</v>
       </c>
-      <c r="DW24" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX24" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV24" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW24" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY24" t="inlineStr">
+        <is>
+          <t>سمك شعور</t>
         </is>
       </c>
     </row>
@@ -6871,14 +6852,19 @@
       <c r="CT25" t="n">
         <v>0</v>
       </c>
-      <c r="DW25" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX25" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV25" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW25" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY25" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -7139,14 +7125,19 @@
       <c r="CT26" t="n">
         <v>0</v>
       </c>
-      <c r="DW26" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX26" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV26" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW26" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY26" t="inlineStr">
+        <is>
+          <t>مياة معبأة</t>
         </is>
       </c>
     </row>
@@ -7392,14 +7383,19 @@
       <c r="CT27" t="n">
         <v>0</v>
       </c>
-      <c r="DW27" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX27" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV27" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW27" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY27" t="inlineStr">
+        <is>
+          <t>مياة غسيل</t>
         </is>
       </c>
     </row>
@@ -7645,14 +7641,19 @@
       <c r="CT28" t="n">
         <v>0</v>
       </c>
-      <c r="DW28" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX28" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV28" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW28" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY28" t="inlineStr">
+        <is>
+          <t>مياة غسيل الاسماك</t>
         </is>
       </c>
     </row>
@@ -7877,14 +7878,19 @@
       <c r="CT29" t="n">
         <v>0</v>
       </c>
-      <c r="DW29" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX29" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV29" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW29" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY29" t="inlineStr">
+        <is>
+          <t>سمك فيلية متبل</t>
         </is>
       </c>
     </row>
@@ -8109,14 +8115,19 @@
       <c r="CT30" t="n">
         <v>0</v>
       </c>
-      <c r="DW30" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX30" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV30" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW30" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY30" t="inlineStr">
+        <is>
+          <t>سمك بلطي</t>
         </is>
       </c>
     </row>
@@ -8341,14 +8352,19 @@
       <c r="CT31" t="n">
         <v>0</v>
       </c>
-      <c r="DW31" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX31" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV31" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW31" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY31" t="inlineStr">
+        <is>
+          <t>سمك دنيس</t>
         </is>
       </c>
     </row>
@@ -8589,14 +8605,24 @@
           <t>Arsenic</t>
         </is>
       </c>
-      <c r="DW32" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX32" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV32" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="CW32" t="inlineStr">
+        <is>
+          <t>أغذية متنوعة</t>
+        </is>
+      </c>
+      <c r="CX32" t="inlineStr">
+        <is>
+          <t>defaulted</t>
+        </is>
+      </c>
+      <c r="CY32" t="inlineStr">
+        <is>
+          <t>ربيان المزرعة</t>
         </is>
       </c>
     </row>
@@ -8821,14 +8847,19 @@
       <c r="CT33" t="n">
         <v>0</v>
       </c>
-      <c r="DW33" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX33" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV33" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW33" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY33" t="inlineStr">
+        <is>
+          <t>سمك شعور</t>
         </is>
       </c>
     </row>
@@ -9053,14 +9084,19 @@
       <c r="CT34" t="n">
         <v>0</v>
       </c>
-      <c r="DW34" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX34" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV34" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW34" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY34" t="inlineStr">
+        <is>
+          <t>سمك هامور</t>
         </is>
       </c>
     </row>
@@ -9285,14 +9321,19 @@
       <c r="CT35" t="n">
         <v>0</v>
       </c>
-      <c r="DW35" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX35" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV35" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW35" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY35" t="inlineStr">
+        <is>
+          <t>سمك بيات</t>
         </is>
       </c>
     </row>
@@ -9517,14 +9558,19 @@
       <c r="CT36" t="n">
         <v>0</v>
       </c>
-      <c r="DW36" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX36" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV36" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW36" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY36" t="inlineStr">
+        <is>
+          <t>سمك قاروص</t>
         </is>
       </c>
     </row>
@@ -9765,14 +9811,24 @@
           <t>Arsenic</t>
         </is>
       </c>
-      <c r="DW37" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX37" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV37" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="CW37" t="inlineStr">
+        <is>
+          <t>أغذية متنوعة</t>
+        </is>
+      </c>
+      <c r="CX37" t="inlineStr">
+        <is>
+          <t>defaulted</t>
+        </is>
+      </c>
+      <c r="CY37" t="inlineStr">
+        <is>
+          <t>ربيان - بحر</t>
         </is>
       </c>
     </row>
@@ -9997,14 +10053,19 @@
       <c r="CT38" t="n">
         <v>0</v>
       </c>
-      <c r="DW38" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX38" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV38" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW38" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY38" t="inlineStr">
+        <is>
+          <t>سمك بوري</t>
         </is>
       </c>
     </row>
@@ -10212,14 +10273,24 @@
       <c r="CT39" t="n">
         <v>0</v>
       </c>
-      <c r="DW39" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX39" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV39" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="CW39" t="inlineStr">
+        <is>
+          <t>أغذية متنوعة</t>
+        </is>
+      </c>
+      <c r="CX39" t="inlineStr">
+        <is>
+          <t>defaulted</t>
+        </is>
+      </c>
+      <c r="CY39" t="inlineStr">
+        <is>
+          <t>سبيط</t>
         </is>
       </c>
     </row>
@@ -10444,14 +10515,19 @@
       <c r="CT40" t="n">
         <v>0</v>
       </c>
-      <c r="DW40" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX40" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV40" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW40" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY40" t="inlineStr">
+        <is>
+          <t>سمك بلطي</t>
         </is>
       </c>
     </row>
@@ -10676,14 +10752,19 @@
       <c r="CT41" t="n">
         <v>0</v>
       </c>
-      <c r="DW41" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX41" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV41" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW41" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY41" t="inlineStr">
+        <is>
+          <t>سمك فيلية</t>
         </is>
       </c>
     </row>
@@ -10908,14 +10989,19 @@
       <c r="CT42" t="n">
         <v>0</v>
       </c>
-      <c r="DW42" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX42" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV42" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW42" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY42" t="inlineStr">
+        <is>
+          <t>سمك ناجل</t>
         </is>
       </c>
     </row>
@@ -11140,14 +11226,19 @@
       <c r="CT43" t="n">
         <v>0</v>
       </c>
-      <c r="DW43" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX43" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV43" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW43" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY43" t="inlineStr">
+        <is>
+          <t>سمك كنعد</t>
         </is>
       </c>
     </row>
@@ -11372,14 +11463,19 @@
       <c r="CT44" t="n">
         <v>0</v>
       </c>
-      <c r="DW44" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX44" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV44" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW44" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY44" t="inlineStr">
+        <is>
+          <t>سمك سلمون</t>
         </is>
       </c>
     </row>
@@ -11643,14 +11739,19 @@
       <c r="CT45" t="n">
         <v>0</v>
       </c>
-      <c r="DW45" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX45" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV45" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW45" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY45" t="inlineStr">
+        <is>
+          <t>مياة معبأة</t>
         </is>
       </c>
     </row>
@@ -11896,14 +11997,19 @@
       <c r="CT46" t="n">
         <v>0</v>
       </c>
-      <c r="DW46" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX46" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV46" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW46" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY46" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -12128,14 +12234,19 @@
       <c r="CT47" t="n">
         <v>0</v>
       </c>
-      <c r="DW47" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX47" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV47" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW47" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY47" t="inlineStr">
+        <is>
+          <t>سمك سلمون</t>
         </is>
       </c>
     </row>
@@ -12360,14 +12471,19 @@
       <c r="CT48" t="n">
         <v>0</v>
       </c>
-      <c r="DW48" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX48" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV48" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW48" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY48" t="inlineStr">
+        <is>
+          <t>سمك دنيس</t>
         </is>
       </c>
     </row>
@@ -12575,14 +12691,19 @@
       <c r="CT49" t="n">
         <v>0</v>
       </c>
-      <c r="DW49" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX49" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV49" t="inlineStr">
+        <is>
+          <t>no_limit</t>
+        </is>
+      </c>
+      <c r="CW49" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY49" t="inlineStr">
+        <is>
+          <t>سمك حبار</t>
         </is>
       </c>
     </row>
@@ -12807,14 +12928,19 @@
       <c r="CT50" t="n">
         <v>0</v>
       </c>
-      <c r="DW50" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX50" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV50" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW50" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY50" t="inlineStr">
+        <is>
+          <t>سمك كنعد</t>
         </is>
       </c>
     </row>
@@ -13039,14 +13165,19 @@
       <c r="CT51" t="n">
         <v>0</v>
       </c>
-      <c r="DW51" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX51" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV51" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW51" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY51" t="inlineStr">
+        <is>
+          <t>سمك سيباس</t>
         </is>
       </c>
     </row>
@@ -13271,14 +13402,19 @@
       <c r="CT52" t="n">
         <v>0</v>
       </c>
-      <c r="DW52" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX52" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV52" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW52" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY52" t="inlineStr">
+        <is>
+          <t>سمك عندق</t>
         </is>
       </c>
     </row>
@@ -13503,14 +13639,19 @@
       <c r="CT53" t="n">
         <v>0</v>
       </c>
-      <c r="DW53" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX53" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV53" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW53" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY53" t="inlineStr">
+        <is>
+          <t>سمك شعور</t>
         </is>
       </c>
     </row>
@@ -13735,14 +13876,19 @@
       <c r="CT54" t="n">
         <v>0</v>
       </c>
-      <c r="DW54" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX54" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV54" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW54" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY54" t="inlineStr">
+        <is>
+          <t>سمك هامور</t>
         </is>
       </c>
     </row>
@@ -13988,14 +14134,19 @@
       <c r="CT55" t="n">
         <v>0</v>
       </c>
-      <c r="DW55" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX55" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV55" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW55" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY55" t="inlineStr">
+        <is>
+          <t>مياة غسيل الاسماك</t>
         </is>
       </c>
     </row>
@@ -14236,14 +14387,24 @@
           <t>Arsenic</t>
         </is>
       </c>
-      <c r="DW56" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX56" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV56" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="CW56" t="inlineStr">
+        <is>
+          <t>أغذية متنوعة</t>
+        </is>
+      </c>
+      <c r="CX56" t="inlineStr">
+        <is>
+          <t>defaulted</t>
+        </is>
+      </c>
+      <c r="CY56" t="inlineStr">
+        <is>
+          <t>ربيان بحر</t>
         </is>
       </c>
     </row>
@@ -14468,14 +14629,19 @@
       <c r="CT57" t="n">
         <v>0</v>
       </c>
-      <c r="DW57" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX57" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV57" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW57" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY57" t="inlineStr">
+        <is>
+          <t>سمك كنعد</t>
         </is>
       </c>
     </row>
@@ -14700,14 +14866,19 @@
       <c r="CT58" t="n">
         <v>0</v>
       </c>
-      <c r="DW58" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX58" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV58" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW58" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY58" t="inlineStr">
+        <is>
+          <t>سمك دنيس</t>
         </is>
       </c>
     </row>
@@ -14932,14 +15103,19 @@
       <c r="CT59" t="n">
         <v>0</v>
       </c>
-      <c r="DW59" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX59" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV59" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW59" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY59" t="inlineStr">
+        <is>
+          <t>سمك شعور</t>
         </is>
       </c>
     </row>
@@ -15164,14 +15340,19 @@
       <c r="CT60" t="n">
         <v>0</v>
       </c>
-      <c r="DW60" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX60" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV60" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW60" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY60" t="inlineStr">
+        <is>
+          <t>سمك عندق</t>
         </is>
       </c>
     </row>
@@ -15396,14 +15577,19 @@
       <c r="CT61" t="n">
         <v>0</v>
       </c>
-      <c r="DW61" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX61" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV61" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW61" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY61" t="inlineStr">
+        <is>
+          <t>سمك هامور</t>
         </is>
       </c>
     </row>
@@ -15628,14 +15814,19 @@
       <c r="CT62" t="n">
         <v>0</v>
       </c>
-      <c r="DW62" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX62" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV62" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW62" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY62" t="inlineStr">
+        <is>
+          <t>سمك عروسة</t>
         </is>
       </c>
     </row>
@@ -15871,14 +16062,24 @@
           <t>Arsenic</t>
         </is>
       </c>
-      <c r="DW63" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX63" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV63" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW63" t="inlineStr">
+        <is>
+          <t>أغذية متنوعة</t>
+        </is>
+      </c>
+      <c r="CX63" t="inlineStr">
+        <is>
+          <t>defaulted</t>
+        </is>
+      </c>
+      <c r="CY63" t="inlineStr">
+        <is>
+          <t>ربيان مزرعة</t>
         </is>
       </c>
     </row>
@@ -16124,14 +16325,19 @@
       <c r="CT64" t="n">
         <v>0</v>
       </c>
-      <c r="DW64" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX64" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV64" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW64" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY64" t="inlineStr">
+        <is>
+          <t>مياه غسيل الاسماك</t>
         </is>
       </c>
     </row>
@@ -16377,14 +16583,19 @@
       <c r="CT65" t="n">
         <v>0</v>
       </c>
-      <c r="DW65" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX65" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV65" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW65" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY65" t="inlineStr">
+        <is>
+          <t>مياه غسيل داوات</t>
         </is>
       </c>
     </row>
@@ -16630,14 +16841,19 @@
       <c r="CT66" t="n">
         <v>0</v>
       </c>
-      <c r="DW66" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX66" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV66" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW66" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY66" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -16883,14 +17099,19 @@
       <c r="CT67" t="n">
         <v>0</v>
       </c>
-      <c r="DW67" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX67" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV67" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW67" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY67" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -17136,14 +17357,19 @@
       <c r="CT68" t="n">
         <v>0</v>
       </c>
-      <c r="DW68" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="DX68" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="CV68" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW68" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY68" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -17389,14 +17615,19 @@
       <c r="CT69" t="n">
         <v>0</v>
       </c>
-      <c r="DW69" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="DX69" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="CV69" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW69" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY69" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -17642,14 +17873,19 @@
       <c r="CT70" t="n">
         <v>0</v>
       </c>
-      <c r="DW70" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="DX70" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="CV70" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW70" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY70" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -17895,14 +18131,19 @@
       <c r="CT71" t="n">
         <v>0</v>
       </c>
-      <c r="DW71" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="DX71" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="CV71" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW71" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY71" t="inlineStr">
+        <is>
+          <t>مياة غسيل حنفية</t>
         </is>
       </c>
     </row>
@@ -18148,14 +18389,19 @@
       <c r="CT72" t="n">
         <v>0</v>
       </c>
-      <c r="DW72" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="DX72" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="CV72" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW72" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY72" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -18401,14 +18647,19 @@
       <c r="CT73" t="n">
         <v>0</v>
       </c>
-      <c r="DW73" t="inlineStr">
-        <is>
-          <t>الروضة</t>
-        </is>
-      </c>
-      <c r="DX73" t="inlineStr">
-        <is>
-          <t>East</t>
+      <c r="CV73" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW73" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY73" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -18630,14 +18881,19 @@
       <c r="CT74" t="n">
         <v>0</v>
       </c>
-      <c r="DW74" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX74" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV74" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW74" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY74" t="inlineStr">
+        <is>
+          <t>مياة حنفية للطبخ</t>
         </is>
       </c>
     </row>
@@ -18859,14 +19115,19 @@
       <c r="CT75" t="n">
         <v>0</v>
       </c>
-      <c r="DW75" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX75" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV75" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW75" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY75" t="inlineStr">
+        <is>
+          <t>مياة غسيل الارز و ادوات التحضير</t>
         </is>
       </c>
     </row>
@@ -19088,14 +19349,19 @@
       <c r="CT76" t="n">
         <v>0</v>
       </c>
-      <c r="DW76" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX76" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV76" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW76" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY76" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -19317,14 +19583,19 @@
       <c r="CT77" t="n">
         <v>0</v>
       </c>
-      <c r="DW77" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX77" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV77" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW77" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY77" t="inlineStr">
+        <is>
+          <t>مياة حنفية</t>
         </is>
       </c>
     </row>
@@ -19546,14 +19817,19 @@
       <c r="CT78" t="n">
         <v>0</v>
       </c>
-      <c r="DW78" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX78" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV78" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW78" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY78" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -19775,14 +20051,19 @@
       <c r="CT79" t="n">
         <v>0</v>
       </c>
-      <c r="DW79" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX79" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV79" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW79" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY79" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -20004,14 +20285,19 @@
       <c r="CT80" t="n">
         <v>0</v>
       </c>
-      <c r="DW80" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX80" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV80" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW80" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY80" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -20233,14 +20519,19 @@
       <c r="CT81" t="n">
         <v>0</v>
       </c>
-      <c r="DW81" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX81" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV81" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW81" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY81" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -20462,14 +20753,19 @@
       <c r="CT82" t="n">
         <v>0</v>
       </c>
-      <c r="DW82" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX82" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV82" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW82" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY82" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -20691,14 +20987,19 @@
       <c r="CT83" t="n">
         <v>0</v>
       </c>
-      <c r="DW83" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX83" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV83" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW83" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY83" t="inlineStr">
+        <is>
+          <t>مياة حنفية للطبخ</t>
         </is>
       </c>
     </row>
@@ -20920,14 +21221,19 @@
       <c r="CT84" t="n">
         <v>0</v>
       </c>
-      <c r="DW84" t="inlineStr">
-        <is>
-          <t>عرقة</t>
-        </is>
-      </c>
-      <c r="DX84" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV84" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW84" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY84" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -21149,14 +21455,19 @@
       <c r="CT85" t="n">
         <v>0</v>
       </c>
-      <c r="DW85" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX85" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV85" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW85" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY85" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -21381,14 +21692,19 @@
       <c r="CT86" t="n">
         <v>0</v>
       </c>
-      <c r="DW86" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX86" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV86" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW86" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY86" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -21610,14 +21926,19 @@
       <c r="CT87" t="n">
         <v>0</v>
       </c>
-      <c r="DW87" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX87" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV87" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW87" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY87" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -21839,14 +22160,19 @@
       <c r="CT88" t="n">
         <v>0</v>
       </c>
-      <c r="DW88" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX88" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV88" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW88" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY88" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -22068,14 +22394,19 @@
       <c r="CT89" t="n">
         <v>0</v>
       </c>
-      <c r="DW89" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX89" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV89" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW89" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY89" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -22297,14 +22628,19 @@
       <c r="CT90" t="n">
         <v>0</v>
       </c>
-      <c r="DW90" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX90" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV90" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW90" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY90" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات ١</t>
         </is>
       </c>
     </row>
@@ -22526,14 +22862,19 @@
       <c r="CT91" t="n">
         <v>0</v>
       </c>
-      <c r="DW91" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX91" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV91" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW91" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY91" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات ٢</t>
         </is>
       </c>
     </row>
@@ -22755,14 +23096,19 @@
       <c r="CT92" t="n">
         <v>0</v>
       </c>
-      <c r="DW92" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX92" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV92" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW92" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY92" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -22984,14 +23330,19 @@
       <c r="CT93" t="n">
         <v>0</v>
       </c>
-      <c r="DW93" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX93" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV93" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW93" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY93" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات ١</t>
         </is>
       </c>
     </row>
@@ -23216,14 +23567,19 @@
       <c r="CT94" t="n">
         <v>0</v>
       </c>
-      <c r="DW94" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX94" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV94" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW94" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY94" t="inlineStr">
+        <is>
+          <t>مياه حنفية لغسيل الادوات ٢</t>
         </is>
       </c>
     </row>
@@ -23450,14 +23806,19 @@
       <c r="CT95" t="n">
         <v>0</v>
       </c>
-      <c r="DW95" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX95" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV95" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="CW95" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY95" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -23682,14 +24043,19 @@
       <c r="CT96" t="n">
         <v>0</v>
       </c>
-      <c r="DW96" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX96" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV96" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW96" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY96" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -23914,14 +24280,19 @@
       <c r="CT97" t="n">
         <v>0</v>
       </c>
-      <c r="DW97" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX97" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV97" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW97" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY97" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -24146,14 +24517,19 @@
       <c r="CT98" t="n">
         <v>0</v>
       </c>
-      <c r="DW98" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX98" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV98" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW98" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY98" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -24378,14 +24754,19 @@
       <c r="CT99" t="n">
         <v>0</v>
       </c>
-      <c r="DW99" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX99" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV99" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW99" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY99" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -24610,14 +24991,19 @@
       <c r="CT100" t="n">
         <v>0</v>
       </c>
-      <c r="DW100" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX100" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV100" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW100" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY100" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -24845,14 +25231,19 @@
       <c r="CT101" t="n">
         <v>0</v>
       </c>
-      <c r="DW101" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX101" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV101" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW101" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY101" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -25077,14 +25468,19 @@
       <c r="CT102" t="n">
         <v>0</v>
       </c>
-      <c r="DW102" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX102" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV102" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW102" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY102" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -25309,14 +25705,19 @@
       <c r="CT103" t="n">
         <v>0</v>
       </c>
-      <c r="DW103" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX103" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV103" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW103" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY103" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -25541,14 +25942,19 @@
       <c r="CT104" t="n">
         <v>0</v>
       </c>
-      <c r="DW104" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX104" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV104" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW104" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY104" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -25776,14 +26182,19 @@
       <c r="CT105" t="n">
         <v>0</v>
       </c>
-      <c r="DW105" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX105" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV105" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW105" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY105" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -26011,14 +26422,19 @@
       <c r="CT106" t="n">
         <v>0</v>
       </c>
-      <c r="DW106" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX106" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV106" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW106" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY106" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -26246,14 +26662,19 @@
       <c r="CT107" t="n">
         <v>0</v>
       </c>
-      <c r="DW107" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX107" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV107" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW107" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY107" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الارز</t>
         </is>
       </c>
     </row>
@@ -26481,14 +26902,19 @@
       <c r="CT108" t="n">
         <v>0</v>
       </c>
-      <c r="DW108" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX108" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV108" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW108" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY108" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -26716,14 +27142,19 @@
       <c r="CT109" t="n">
         <v>0</v>
       </c>
-      <c r="DW109" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX109" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV109" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW109" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY109" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -26954,14 +27385,19 @@
       <c r="CT110" t="n">
         <v>0</v>
       </c>
-      <c r="DW110" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX110" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV110" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW110" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY110" t="inlineStr">
+        <is>
+          <t>مياه حنفية للعجانة</t>
         </is>
       </c>
     </row>
@@ -27192,14 +27628,19 @@
       <c r="CT111" t="n">
         <v>0</v>
       </c>
-      <c r="DW111" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX111" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV111" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW111" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY111" t="inlineStr">
+        <is>
+          <t>مياه حنفية غسيل ادوات</t>
         </is>
       </c>
     </row>
@@ -27430,14 +27871,19 @@
       <c r="CT112" t="n">
         <v>0</v>
       </c>
-      <c r="DW112" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX112" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV112" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW112" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY112" t="inlineStr">
+        <is>
+          <t>مياه غسيل الاسماك</t>
         </is>
       </c>
     </row>
@@ -27663,14 +28109,24 @@
           <t>Arsenic</t>
         </is>
       </c>
-      <c r="DW113" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX113" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV113" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="CW113" t="inlineStr">
+        <is>
+          <t>أغذية متنوعة</t>
+        </is>
+      </c>
+      <c r="CX113" t="inlineStr">
+        <is>
+          <t>defaulted</t>
+        </is>
+      </c>
+      <c r="CY113" t="inlineStr">
+        <is>
+          <t>ربيان مزرعة</t>
         </is>
       </c>
     </row>
@@ -27896,14 +28352,24 @@
           <t>Arsenic</t>
         </is>
       </c>
-      <c r="DW114" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX114" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV114" t="inlineStr">
+        <is>
+          <t>invalid</t>
+        </is>
+      </c>
+      <c r="CW114" t="inlineStr">
+        <is>
+          <t>أغذية متنوعة</t>
+        </is>
+      </c>
+      <c r="CX114" t="inlineStr">
+        <is>
+          <t>defaulted</t>
+        </is>
+      </c>
+      <c r="CY114" t="inlineStr">
+        <is>
+          <t>ربيان بحري</t>
         </is>
       </c>
     </row>
@@ -28113,14 +28579,19 @@
       <c r="CT115" t="n">
         <v>0</v>
       </c>
-      <c r="DW115" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX115" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV115" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW115" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY115" t="inlineStr">
+        <is>
+          <t>سمك كنعد</t>
         </is>
       </c>
     </row>
@@ -28330,14 +28801,19 @@
       <c r="CT116" t="n">
         <v>0</v>
       </c>
-      <c r="DW116" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX116" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV116" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW116" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY116" t="inlineStr">
+        <is>
+          <t>سمك سالمون</t>
         </is>
       </c>
     </row>
@@ -28547,14 +29023,19 @@
       <c r="CT117" t="n">
         <v>0</v>
       </c>
-      <c r="DW117" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX117" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV117" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW117" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY117" t="inlineStr">
+        <is>
+          <t>سمك بلطي</t>
         </is>
       </c>
     </row>
@@ -28779,14 +29260,19 @@
       <c r="CT118" t="n">
         <v>0</v>
       </c>
-      <c r="DW118" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX118" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV118" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW118" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY118" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -29011,14 +29497,19 @@
       <c r="CT119" t="n">
         <v>0</v>
       </c>
-      <c r="DW119" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX119" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV119" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW119" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY119" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الأدوات</t>
         </is>
       </c>
     </row>
@@ -29246,14 +29737,19 @@
       <c r="CT120" t="n">
         <v>0</v>
       </c>
-      <c r="DW120" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX120" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV120" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW120" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY120" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الأدوات(1)</t>
         </is>
       </c>
     </row>
@@ -29478,14 +29974,19 @@
       <c r="CT121" t="n">
         <v>0</v>
       </c>
-      <c r="DW121" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX121" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV121" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW121" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY121" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الأدوات(2)</t>
         </is>
       </c>
     </row>
@@ -29719,14 +30220,19 @@
       <c r="CT122" t="n">
         <v>0</v>
       </c>
-      <c r="DW122" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX122" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV122" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW122" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY122" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -29960,14 +30466,19 @@
       <c r="CT123" t="n">
         <v>0</v>
       </c>
-      <c r="DW123" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX123" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV123" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW123" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY123" t="inlineStr">
+        <is>
+          <t>مياة حنفية غسيل</t>
         </is>
       </c>
     </row>
@@ -30201,14 +30712,19 @@
       <c r="CT124" t="n">
         <v>0</v>
       </c>
-      <c r="DW124" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX124" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV124" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW124" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY124" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -30442,14 +30958,19 @@
       <c r="CT125" t="n">
         <v>0</v>
       </c>
-      <c r="DW125" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX125" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV125" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW125" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY125" t="inlineStr">
+        <is>
+          <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -30683,14 +31204,19 @@
       <c r="CT126" t="n">
         <v>0</v>
       </c>
-      <c r="DW126" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX126" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV126" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW126" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY126" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -30924,14 +31450,19 @@
       <c r="CT127" t="n">
         <v>0</v>
       </c>
-      <c r="DW127" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX127" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV127" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW127" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY127" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -31162,14 +31693,19 @@
       <c r="CT128" t="n">
         <v>0</v>
       </c>
-      <c r="DW128" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX128" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV128" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW128" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY128" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -31400,14 +31936,19 @@
       <c r="CT129" t="n">
         <v>0</v>
       </c>
-      <c r="DW129" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX129" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV129" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW129" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY129" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -31638,14 +32179,19 @@
       <c r="CT130" t="n">
         <v>0</v>
       </c>
-      <c r="DW130" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX130" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV130" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW130" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY130" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -31876,14 +32422,19 @@
       <c r="CT131" t="n">
         <v>0</v>
       </c>
-      <c r="DW131" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX131" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV131" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW131" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY131" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -32114,14 +32665,19 @@
       <c r="CT132" t="n">
         <v>0</v>
       </c>
-      <c r="DW132" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX132" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV132" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW132" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY132" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -32352,14 +32908,19 @@
       <c r="CT133" t="n">
         <v>0</v>
       </c>
-      <c r="DW133" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX133" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV133" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW133" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY133" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -32590,14 +33151,19 @@
       <c r="CT134" t="n">
         <v>0</v>
       </c>
-      <c r="DW134" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX134" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV134" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW134" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY134" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -32828,14 +33394,19 @@
       <c r="CT135" t="n">
         <v>0</v>
       </c>
-      <c r="DW135" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX135" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV135" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW135" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY135" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -33066,14 +33637,19 @@
       <c r="CT136" t="n">
         <v>0</v>
       </c>
-      <c r="DW136" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX136" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV136" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW136" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY136" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -33304,14 +33880,19 @@
       <c r="CT137" t="n">
         <v>0</v>
       </c>
-      <c r="DW137" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX137" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV137" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW137" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY137" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -33542,14 +34123,19 @@
       <c r="CT138" t="n">
         <v>0</v>
       </c>
-      <c r="DW138" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX138" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV138" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW138" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY138" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -33780,14 +34366,19 @@
       <c r="CT139" t="n">
         <v>0</v>
       </c>
-      <c r="DW139" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX139" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV139" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW139" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY139" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -34018,14 +34609,19 @@
       <c r="CT140" t="n">
         <v>0</v>
       </c>
-      <c r="DW140" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX140" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV140" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW140" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY140" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -34256,14 +34852,19 @@
       <c r="CT141" t="n">
         <v>0</v>
       </c>
-      <c r="DW141" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX141" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV141" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW141" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY141" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -34494,14 +35095,19 @@
       <c r="CT142" t="n">
         <v>0</v>
       </c>
-      <c r="DW142" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX142" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV142" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW142" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY142" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -34732,14 +35338,19 @@
       <c r="CT143" t="n">
         <v>0</v>
       </c>
-      <c r="DW143" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX143" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV143" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW143" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY143" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -34970,14 +35581,19 @@
       <c r="CT144" t="n">
         <v>0</v>
       </c>
-      <c r="DW144" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX144" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV144" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW144" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY144" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -35208,14 +35824,19 @@
       <c r="CT145" t="n">
         <v>0</v>
       </c>
-      <c r="DW145" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX145" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV145" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW145" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY145" t="inlineStr">
+        <is>
+          <t>مياة حنفية</t>
         </is>
       </c>
     </row>
@@ -35446,14 +36067,19 @@
       <c r="CT146" t="n">
         <v>0</v>
       </c>
-      <c r="DW146" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX146" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV146" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW146" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY146" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الارز</t>
         </is>
       </c>
     </row>
@@ -35684,14 +36310,19 @@
       <c r="CT147" t="n">
         <v>0</v>
       </c>
-      <c r="DW147" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX147" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV147" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW147" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY147" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -35922,14 +36553,19 @@
       <c r="CT148" t="n">
         <v>0</v>
       </c>
-      <c r="DW148" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX148" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV148" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW148" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY148" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -36169,14 +36805,19 @@
       <c r="CT149" t="n">
         <v>0</v>
       </c>
-      <c r="DW149" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX149" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV149" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW149" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY149" t="inlineStr">
+        <is>
+          <t>مياة معبأة للطبخ</t>
         </is>
       </c>
     </row>
@@ -36416,14 +37057,19 @@
       <c r="CT150" t="n">
         <v>0</v>
       </c>
-      <c r="DW150" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX150" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV150" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW150" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY150" t="inlineStr">
+        <is>
+          <t>مياة معبأة للعجانة</t>
         </is>
       </c>
     </row>
@@ -36654,14 +37300,19 @@
       <c r="CT151" t="n">
         <v>0</v>
       </c>
-      <c r="DW151" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX151" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV151" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW151" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY151" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -36892,14 +37543,19 @@
       <c r="CT152" t="n">
         <v>0</v>
       </c>
-      <c r="DW152" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX152" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV152" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW152" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY152" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -37130,14 +37786,19 @@
       <c r="CT153" t="n">
         <v>0</v>
       </c>
-      <c r="DW153" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX153" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV153" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW153" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY153" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -37368,14 +38029,19 @@
       <c r="CT154" t="n">
         <v>0</v>
       </c>
-      <c r="DW154" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX154" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV154" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW154" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY154" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -37606,14 +38272,19 @@
       <c r="CT155" t="n">
         <v>0</v>
       </c>
-      <c r="DW155" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX155" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV155" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW155" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY155" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -37844,14 +38515,19 @@
       <c r="CT156" t="n">
         <v>0</v>
       </c>
-      <c r="DW156" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX156" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV156" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW156" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY156" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -38082,14 +38758,19 @@
       <c r="CT157" t="n">
         <v>0</v>
       </c>
-      <c r="DW157" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX157" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV157" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW157" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY157" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -38323,14 +39004,19 @@
       <c r="CT158" t="n">
         <v>0</v>
       </c>
-      <c r="DW158" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX158" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV158" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW158" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY158" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -38564,14 +39250,19 @@
       <c r="CT159" t="n">
         <v>0</v>
       </c>
-      <c r="DW159" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX159" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV159" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW159" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY159" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -38805,14 +39496,19 @@
       <c r="CT160" t="n">
         <v>0</v>
       </c>
-      <c r="DW160" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX160" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV160" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW160" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY160" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
     </row>
@@ -39046,14 +39742,19 @@
       <c r="CT161" t="n">
         <v>0</v>
       </c>
-      <c r="DW161" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX161" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV161" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW161" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY161" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -39287,14 +39988,19 @@
       <c r="CT162" t="n">
         <v>0</v>
       </c>
-      <c r="DW162" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX162" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV162" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW162" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY162" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -39528,14 +40234,19 @@
       <c r="CT163" t="n">
         <v>0</v>
       </c>
-      <c r="DW163" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX163" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV163" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW163" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY163" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -39769,14 +40480,19 @@
       <c r="CT164" t="n">
         <v>0</v>
       </c>
-      <c r="DW164" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX164" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV164" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW164" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY164" t="inlineStr">
+        <is>
+          <t>مياه غسيل أدوات</t>
         </is>
       </c>
     </row>
@@ -40010,14 +40726,19 @@
       <c r="CT165" t="n">
         <v>0</v>
       </c>
-      <c r="DW165" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX165" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV165" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW165" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY165" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -40260,14 +40981,19 @@
       <c r="CT166" t="n">
         <v>0</v>
       </c>
-      <c r="DW166" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX166" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV166" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW166" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY166" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -40501,14 +41227,19 @@
       <c r="CT167" t="n">
         <v>0</v>
       </c>
-      <c r="DW167" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX167" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV167" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW167" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY167" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -40742,14 +41473,19 @@
       <c r="CT168" t="n">
         <v>0</v>
       </c>
-      <c r="DW168" t="inlineStr">
-        <is>
-          <t>المعذر</t>
-        </is>
-      </c>
-      <c r="DX168" t="inlineStr">
-        <is>
-          <t>Central</t>
+      <c r="CV168" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW168" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY168" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -40983,14 +41719,19 @@
       <c r="CT169" t="n">
         <v>0</v>
       </c>
-      <c r="DW169" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX169" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV169" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW169" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY169" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات - ك</t>
         </is>
       </c>
     </row>
@@ -41224,14 +41965,19 @@
       <c r="CT170" t="n">
         <v>0</v>
       </c>
-      <c r="DW170" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX170" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV170" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW170" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY170" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -41465,14 +42211,19 @@
       <c r="CT171" t="n">
         <v>0</v>
       </c>
-      <c r="DW171" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX171" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV171" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW171" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY171" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -41706,14 +42457,19 @@
       <c r="CT172" t="n">
         <v>0</v>
       </c>
-      <c r="DW172" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX172" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV172" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW172" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY172" t="inlineStr">
+        <is>
+          <t>مياة حنفية للطبخ م.ك</t>
         </is>
       </c>
     </row>
@@ -41947,14 +42703,19 @@
       <c r="CT173" t="n">
         <v>0</v>
       </c>
-      <c r="DW173" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX173" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV173" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW173" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY173" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -42188,14 +42949,19 @@
       <c r="CT174" t="n">
         <v>0</v>
       </c>
-      <c r="DW174" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX174" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV174" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW174" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY174" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -42429,14 +43195,19 @@
       <c r="CT175" t="n">
         <v>0</v>
       </c>
-      <c r="DW175" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX175" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV175" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW175" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY175" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -42670,9 +43441,19 @@
       <c r="CT176" t="n">
         <v>0</v>
       </c>
-      <c r="DW176" t="inlineStr">
-        <is>
-          <t>عينة خاصة</t>
+      <c r="CV176" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW176" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY176" t="inlineStr">
+        <is>
+          <t>A مياة</t>
         </is>
       </c>
     </row>
@@ -42906,9 +43687,19 @@
       <c r="CT177" t="n">
         <v>0</v>
       </c>
-      <c r="DW177" t="inlineStr">
-        <is>
-          <t>عينة خاصة</t>
+      <c r="CV177" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW177" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY177" t="inlineStr">
+        <is>
+          <t>B مياة</t>
         </is>
       </c>
     </row>
@@ -43142,9 +43933,19 @@
       <c r="CT178" t="n">
         <v>0</v>
       </c>
-      <c r="DW178" t="inlineStr">
-        <is>
-          <t>عينة خاصة</t>
+      <c r="CV178" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW178" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY178" t="inlineStr">
+        <is>
+          <t>C مياة</t>
         </is>
       </c>
     </row>
@@ -43378,14 +44179,19 @@
       <c r="CT179" t="n">
         <v>0</v>
       </c>
-      <c r="DW179" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX179" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV179" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW179" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY179" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
     </row>
@@ -43619,14 +44425,19 @@
       <c r="CT180" t="n">
         <v>0</v>
       </c>
-      <c r="DW180" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX180" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV180" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW180" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY180" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -43860,14 +44671,19 @@
       <c r="CT181" t="n">
         <v>0</v>
       </c>
-      <c r="DW181" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX181" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV181" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW181" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY181" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -44110,14 +44926,19 @@
       <c r="CT182" t="n">
         <v>0</v>
       </c>
-      <c r="DW182" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX182" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV182" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW182" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY182" t="inlineStr">
+        <is>
+          <t>مياة معبأة للطبخ م.ك</t>
         </is>
       </c>
     </row>
@@ -44351,14 +45172,19 @@
       <c r="CT183" t="n">
         <v>0</v>
       </c>
-      <c r="DW183" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX183" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV183" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW183" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY183" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -44592,14 +45418,19 @@
       <c r="CT184" t="n">
         <v>0</v>
       </c>
-      <c r="DW184" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX184" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV184" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW184" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY184" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -44833,14 +45664,19 @@
       <c r="CT185" t="n">
         <v>0</v>
       </c>
-      <c r="DW185" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX185" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV185" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW185" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY185" t="inlineStr">
+        <is>
+          <t>موية غسيل ادوات</t>
         </is>
       </c>
     </row>
@@ -45074,14 +45910,19 @@
       <c r="CT186" t="n">
         <v>0</v>
       </c>
-      <c r="DW186" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX186" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV186" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW186" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY186" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -45315,14 +46156,19 @@
       <c r="CT187" t="n">
         <v>0</v>
       </c>
-      <c r="DW187" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX187" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV187" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW187" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY187" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -45556,14 +46402,19 @@
       <c r="CT188" t="n">
         <v>0</v>
       </c>
-      <c r="DW188" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX188" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV188" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW188" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY188" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -45797,14 +46648,19 @@
       <c r="CT189" t="n">
         <v>0</v>
       </c>
-      <c r="DW189" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX189" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV189" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW189" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY189" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -46038,14 +46894,19 @@
       <c r="CT190" t="n">
         <v>0</v>
       </c>
-      <c r="DW190" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX190" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV190" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW190" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY190" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -46282,14 +47143,19 @@
       <c r="CT191" t="n">
         <v>0</v>
       </c>
-      <c r="DW191" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX191" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV191" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW191" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY191" t="inlineStr">
+        <is>
+          <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
     </row>
@@ -46526,14 +47392,19 @@
       <c r="CT192" t="n">
         <v>0</v>
       </c>
-      <c r="DW192" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX192" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV192" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW192" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY192" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -46770,14 +47641,19 @@
       <c r="CT193" t="n">
         <v>0</v>
       </c>
-      <c r="DW193" t="inlineStr">
-        <is>
-          <t>نمار</t>
-        </is>
-      </c>
-      <c r="DX193" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV193" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW193" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY193" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -47014,14 +47890,19 @@
       <c r="CT194" t="n">
         <v>0</v>
       </c>
-      <c r="DW194" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX194" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV194" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW194" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY194" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -47258,14 +48139,19 @@
       <c r="CT195" t="n">
         <v>0</v>
       </c>
-      <c r="DW195" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX195" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV195" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW195" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY195" t="inlineStr">
+        <is>
+          <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
     </row>
@@ -47502,14 +48388,19 @@
       <c r="CT196" t="n">
         <v>0</v>
       </c>
-      <c r="DW196" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX196" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV196" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW196" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY196" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -47746,14 +48637,19 @@
       <c r="CT197" t="n">
         <v>0</v>
       </c>
-      <c r="DW197" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX197" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV197" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW197" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY197" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -47990,14 +48886,19 @@
       <c r="CT198" t="n">
         <v>0</v>
       </c>
-      <c r="DW198" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX198" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV198" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW198" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY198" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
     </row>
@@ -48234,14 +49135,19 @@
       <c r="CT199" t="n">
         <v>0</v>
       </c>
-      <c r="DW199" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX199" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV199" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW199" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY199" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -48478,14 +49384,19 @@
       <c r="CT200" t="n">
         <v>0</v>
       </c>
-      <c r="DW200" t="inlineStr">
-        <is>
-          <t>الشميسي</t>
-        </is>
-      </c>
-      <c r="DX200" t="inlineStr">
-        <is>
-          <t>Central</t>
+      <c r="CV200" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW200" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY200" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -48722,14 +49633,19 @@
       <c r="CT201" t="n">
         <v>0</v>
       </c>
-      <c r="DW201" t="inlineStr">
-        <is>
-          <t>الشميسي</t>
-        </is>
-      </c>
-      <c r="DX201" t="inlineStr">
-        <is>
-          <t>Central</t>
+      <c r="CV201" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW201" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY201" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -48966,14 +49882,19 @@
       <c r="CT202" t="n">
         <v>0</v>
       </c>
-      <c r="DW202" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX202" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV202" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW202" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY202" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -49210,14 +50131,19 @@
       <c r="CT203" t="n">
         <v>0</v>
       </c>
-      <c r="DW203" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX203" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV203" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW203" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY203" t="inlineStr">
+        <is>
+          <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
     </row>
@@ -49454,14 +50380,19 @@
       <c r="CT204" t="n">
         <v>0</v>
       </c>
-      <c r="DW204" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX204" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV204" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW204" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY204" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -49692,14 +50623,19 @@
       <c r="CT205" t="n">
         <v>0</v>
       </c>
-      <c r="DW205" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX205" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV205" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW205" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY205" t="inlineStr">
+        <is>
+          <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
     </row>
@@ -49933,14 +50869,19 @@
       <c r="CT206" t="n">
         <v>0</v>
       </c>
-      <c r="DW206" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX206" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV206" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW206" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY206" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -50174,14 +51115,19 @@
       <c r="CT207" t="n">
         <v>0</v>
       </c>
-      <c r="DW207" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX207" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV207" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW207" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY207" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -50420,14 +51366,19 @@
           <t>Lead</t>
         </is>
       </c>
-      <c r="DW208" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX208" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV208" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW208" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY208" t="inlineStr">
+        <is>
+          <t>مياة حنفية م.ك</t>
         </is>
       </c>
     </row>
@@ -50661,14 +51612,19 @@
       <c r="CT209" t="n">
         <v>0</v>
       </c>
-      <c r="DW209" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX209" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV209" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW209" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY209" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -50902,14 +51858,19 @@
       <c r="CT210" t="n">
         <v>0</v>
       </c>
-      <c r="DW210" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX210" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV210" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW210" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY210" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الاسماك م.ك</t>
         </is>
       </c>
     </row>
@@ -51143,14 +52104,19 @@
       <c r="CT211" t="n">
         <v>0</v>
       </c>
-      <c r="DW211" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX211" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV211" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW211" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY211" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
     </row>
@@ -51384,14 +52350,19 @@
       <c r="CT212" t="n">
         <v>0</v>
       </c>
-      <c r="DW212" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX212" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV212" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW212" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY212" t="inlineStr">
+        <is>
+          <t>مياةحنفية للغسيل م.ك</t>
         </is>
       </c>
     </row>
@@ -51604,14 +52575,19 @@
       <c r="CT213" t="n">
         <v>0</v>
       </c>
-      <c r="DW213" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX213" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV213" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW213" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY213" t="inlineStr">
+        <is>
+          <t>سمك دنيس ني م.ك</t>
         </is>
       </c>
     </row>
@@ -51824,14 +52800,19 @@
       <c r="CT214" t="n">
         <v>0</v>
       </c>
-      <c r="DW214" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX214" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV214" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW214" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY214" t="inlineStr">
+        <is>
+          <t>سمك سلمون ني م.ك</t>
         </is>
       </c>
     </row>
@@ -52044,14 +53025,19 @@
       <c r="CT215" t="n">
         <v>0</v>
       </c>
-      <c r="DW215" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX215" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV215" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW215" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
+      <c r="CY215" t="inlineStr">
+        <is>
+          <t>سمك كنعد ني م.ك</t>
         </is>
       </c>
     </row>
@@ -52280,14 +53266,19 @@
       <c r="CT216" t="n">
         <v>0</v>
       </c>
-      <c r="DW216" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX216" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV216" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW216" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY216" t="inlineStr">
+        <is>
+          <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
     </row>
@@ -52525,14 +53516,19 @@
       <c r="CT217" t="n">
         <v>0</v>
       </c>
-      <c r="DW217" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX217" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV217" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW217" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY217" t="inlineStr">
+        <is>
+          <t>مياه معاباة للطبخ</t>
         </is>
       </c>
     </row>
@@ -52761,14 +53757,19 @@
       <c r="CT218" t="n">
         <v>0</v>
       </c>
-      <c r="DW218" t="inlineStr">
-        <is>
-          <t>العريجاء</t>
-        </is>
-      </c>
-      <c r="DX218" t="inlineStr">
-        <is>
-          <t>West</t>
+      <c r="CV218" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW218" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY218" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -52997,14 +53998,19 @@
       <c r="CT219" t="n">
         <v>0</v>
       </c>
-      <c r="DW219" t="inlineStr">
-        <is>
-          <t>الشميسي</t>
-        </is>
-      </c>
-      <c r="DX219" t="inlineStr">
-        <is>
-          <t>Central</t>
+      <c r="CV219" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW219" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
+        </is>
+      </c>
+      <c r="CY219" t="inlineStr">
+        <is>
+          <t>مياه فلتر</t>
         </is>
       </c>
     </row>
@@ -53225,6 +54231,21 @@
       <c r="CT220" t="n">
         <v>0</v>
       </c>
+      <c r="CV220" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW220" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY220" t="inlineStr">
+        <is>
+          <t>مياه حنفيه لغسيل الارز</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -53443,9 +54464,24 @@
       <c r="CT221" t="n">
         <v>0</v>
       </c>
+      <c r="CV221" t="inlineStr">
+        <is>
+          <t>valid</t>
+        </is>
+      </c>
+      <c r="CW221" t="inlineStr">
+        <is>
+          <t>مياه الحنفية</t>
+        </is>
+      </c>
+      <c r="CY221" t="inlineStr">
+        <is>
+          <t>مياه حنفيه لغسيل الادوات</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:DX221"/>
+  <autoFilter ref="A1:CZ221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -53456,7 +54492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:D109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -53482,7 +54518,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Columns: 128</t>
+          <t>Columns: 104</t>
         </is>
       </c>
     </row>
@@ -55225,63 +56261,79 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>qc_for_invalid</t>
+          <t>validity_status</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="C105" t="n">
-        <v>220</v>
-      </c>
-      <c r="D105" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>valid | valid | invalid</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>qc_result</t>
+          <t>sample_category_canonical</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="C106" t="n">
-        <v>220</v>
-      </c>
-      <c r="D106" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>الأسماك والمأكولات البحرية | الأسماك والمأكولات البحرية | الأسماك والمأكولات البحرية</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>silver_qc</t>
+          <t>category_flag</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="C107" t="n">
-        <v>220</v>
-      </c>
-      <c r="D107" t="inlineStr"/>
+        <v>211</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>defaulted | defaulted | defaulted</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>aluminum_qc</t>
+          <t>sample_name_group</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0</v>
+        <v>220</v>
       </c>
       <c r="C108" t="n">
-        <v>220</v>
-      </c>
-      <c r="D108" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>سمك بلطي ني | سمك بوري ني | جمبري وسط ني</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>arsenic_qc</t>
+          <t>sample_code</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -55291,350 +56343,6 @@
         <v>220</v>
       </c>
       <c r="D109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>barium_qc</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>0</v>
-      </c>
-      <c r="C110" t="n">
-        <v>220</v>
-      </c>
-      <c r="D110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>beryllium_qc</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>0</v>
-      </c>
-      <c r="C111" t="n">
-        <v>220</v>
-      </c>
-      <c r="D111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>cadmium_qc</t>
-        </is>
-      </c>
-      <c r="B112" t="n">
-        <v>0</v>
-      </c>
-      <c r="C112" t="n">
-        <v>220</v>
-      </c>
-      <c r="D112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>cobalt_qc</t>
-        </is>
-      </c>
-      <c r="B113" t="n">
-        <v>0</v>
-      </c>
-      <c r="C113" t="n">
-        <v>220</v>
-      </c>
-      <c r="D113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>chromium_qc</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>0</v>
-      </c>
-      <c r="C114" t="n">
-        <v>220</v>
-      </c>
-      <c r="D114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>cesium_qc</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0</v>
-      </c>
-      <c r="C115" t="n">
-        <v>220</v>
-      </c>
-      <c r="D115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>copper_qc</t>
-        </is>
-      </c>
-      <c r="B116" t="n">
-        <v>0</v>
-      </c>
-      <c r="C116" t="n">
-        <v>220</v>
-      </c>
-      <c r="D116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>iron_qc</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>0</v>
-      </c>
-      <c r="C117" t="n">
-        <v>220</v>
-      </c>
-      <c r="D117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>manganese_qc</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>0</v>
-      </c>
-      <c r="C118" t="n">
-        <v>220</v>
-      </c>
-      <c r="D118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>nickel_qc</t>
-        </is>
-      </c>
-      <c r="B119" t="n">
-        <v>0</v>
-      </c>
-      <c r="C119" t="n">
-        <v>220</v>
-      </c>
-      <c r="D119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>lead_qc</t>
-        </is>
-      </c>
-      <c r="B120" t="n">
-        <v>0</v>
-      </c>
-      <c r="C120" t="n">
-        <v>220</v>
-      </c>
-      <c r="D120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>rubidium_qc</t>
-        </is>
-      </c>
-      <c r="B121" t="n">
-        <v>0</v>
-      </c>
-      <c r="C121" t="n">
-        <v>220</v>
-      </c>
-      <c r="D121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>selenium_qc</t>
-        </is>
-      </c>
-      <c r="B122" t="n">
-        <v>0</v>
-      </c>
-      <c r="C122" t="n">
-        <v>220</v>
-      </c>
-      <c r="D122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>strontium_qc</t>
-        </is>
-      </c>
-      <c r="B123" t="n">
-        <v>0</v>
-      </c>
-      <c r="C123" t="n">
-        <v>220</v>
-      </c>
-      <c r="D123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>uranium_qc</t>
-        </is>
-      </c>
-      <c r="B124" t="n">
-        <v>0</v>
-      </c>
-      <c r="C124" t="n">
-        <v>220</v>
-      </c>
-      <c r="D124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>mercury_qc</t>
-        </is>
-      </c>
-      <c r="B125" t="n">
-        <v>0</v>
-      </c>
-      <c r="C125" t="n">
-        <v>220</v>
-      </c>
-      <c r="D125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>vanadium_qc</t>
-        </is>
-      </c>
-      <c r="B126" t="n">
-        <v>0</v>
-      </c>
-      <c r="C126" t="n">
-        <v>220</v>
-      </c>
-      <c r="D126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>zinc_qc</t>
-        </is>
-      </c>
-      <c r="B127" t="n">
-        <v>0</v>
-      </c>
-      <c r="C127" t="n">
-        <v>220</v>
-      </c>
-      <c r="D127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>calcium_qc</t>
-        </is>
-      </c>
-      <c r="B128" t="n">
-        <v>0</v>
-      </c>
-      <c r="C128" t="n">
-        <v>220</v>
-      </c>
-      <c r="D128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>potassium_qc</t>
-        </is>
-      </c>
-      <c r="B129" t="n">
-        <v>0</v>
-      </c>
-      <c r="C129" t="n">
-        <v>220</v>
-      </c>
-      <c r="D129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>magnesium_qc</t>
-        </is>
-      </c>
-      <c r="B130" t="n">
-        <v>0</v>
-      </c>
-      <c r="C130" t="n">
-        <v>220</v>
-      </c>
-      <c r="D130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>sodium_qc</t>
-        </is>
-      </c>
-      <c r="B131" t="n">
-        <v>0</v>
-      </c>
-      <c r="C131" t="n">
-        <v>220</v>
-      </c>
-      <c r="D131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>municipality_canonical</t>
-        </is>
-      </c>
-      <c r="B132" t="n">
-        <v>218</v>
-      </c>
-      <c r="C132" t="n">
-        <v>2</v>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>عرقة | عرقة | عرقة</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>sector</t>
-        </is>
-      </c>
-      <c r="B133" t="n">
-        <v>215</v>
-      </c>
-      <c r="C133" t="n">
-        <v>5</v>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>West | West | West</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/clean/chemistry/chem_heavy_metals_2024.xlsx
+++ b/clean/chemistry/chem_heavy_metals_2024.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$CZ$221</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'data'!$A$1:$DB$221</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ221"/>
+  <dimension ref="A1:DB221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -547,7 +547,9 @@
     <col width="28" customWidth="1" min="101" max="101"/>
     <col width="15" customWidth="1" min="102" max="102"/>
     <col width="33" customWidth="1" min="103" max="103"/>
-    <col width="13" customWidth="1" min="104" max="104"/>
+    <col width="29" customWidth="1" min="104" max="104"/>
+    <col width="17" customWidth="1" min="105" max="105"/>
+    <col width="13" customWidth="1" min="106" max="106"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -1068,6 +1070,16 @@
       </c>
       <c r="CZ1" s="1" t="inlineStr">
         <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>sector_flag</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
           <t>sample_code</t>
         </is>
       </c>
@@ -1308,6 +1320,11 @@
           <t>سمك بلطي ني</t>
         </is>
       </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1545,6 +1562,11 @@
           <t>سمك بوري ني</t>
         </is>
       </c>
+      <c r="CZ3" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1798,6 +1820,11 @@
           <t>جمبري وسط ني</t>
         </is>
       </c>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2035,6 +2062,11 @@
           <t>سمك سلمون ني</t>
         </is>
       </c>
+      <c r="CZ5" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2272,6 +2304,11 @@
           <t>سمك دنيس ني</t>
         </is>
       </c>
+      <c r="CZ6" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2509,6 +2546,11 @@
           <t>سمك شعور ني</t>
         </is>
       </c>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2746,6 +2788,11 @@
           <t>سمك كنعد ني</t>
         </is>
       </c>
+      <c r="CZ8" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2983,6 +3030,11 @@
           <t>سمك دنيس ني</t>
         </is>
       </c>
+      <c r="CZ9" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3220,6 +3272,11 @@
           <t>سمك بوري ني</t>
         </is>
       </c>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3478,6 +3535,11 @@
           <t>مياة سخان</t>
         </is>
       </c>
+      <c r="CZ11" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3736,6 +3798,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ12" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3994,6 +4061,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ13" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4247,6 +4319,11 @@
           <t>جمبري وسط - مزارع</t>
         </is>
       </c>
+      <c r="CZ14" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4500,6 +4577,11 @@
           <t>جمبري وسط - بحر</t>
         </is>
       </c>
+      <c r="CZ15" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4737,6 +4819,11 @@
           <t>السمك بوري</t>
         </is>
       </c>
+      <c r="CZ16" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4974,6 +5061,11 @@
           <t>سمك دنيس</t>
         </is>
       </c>
+      <c r="CZ17" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5211,6 +5303,11 @@
           <t>سمك بلطي</t>
         </is>
       </c>
+      <c r="CZ18" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5448,6 +5545,11 @@
           <t>سمك سلمون</t>
         </is>
       </c>
+      <c r="CZ19" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5673,6 +5775,11 @@
           <t>محار</t>
         </is>
       </c>
+      <c r="CZ20" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5898,6 +6005,11 @@
           <t>كابوريا</t>
         </is>
       </c>
+      <c r="CZ21" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -6135,6 +6247,11 @@
           <t>سمك اروص</t>
         </is>
       </c>
+      <c r="CZ22" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -6372,6 +6489,11 @@
           <t>سمك هامور</t>
         </is>
       </c>
+      <c r="CZ23" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -6609,6 +6731,11 @@
           <t>سمك شعور</t>
         </is>
       </c>
+      <c r="CZ24" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6867,6 +6994,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ25" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -7140,6 +7272,11 @@
           <t>مياة معبأة</t>
         </is>
       </c>
+      <c r="CZ26" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -7398,6 +7535,11 @@
           <t>مياة غسيل</t>
         </is>
       </c>
+      <c r="CZ27" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -7656,6 +7798,11 @@
           <t>مياة غسيل الاسماك</t>
         </is>
       </c>
+      <c r="CZ28" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -7893,6 +8040,11 @@
           <t>سمك فيلية متبل</t>
         </is>
       </c>
+      <c r="CZ29" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -8130,6 +8282,11 @@
           <t>سمك بلطي</t>
         </is>
       </c>
+      <c r="CZ30" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -8367,6 +8524,11 @@
           <t>سمك دنيس</t>
         </is>
       </c>
+      <c r="CZ31" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -8625,6 +8787,11 @@
           <t>ربيان المزرعة</t>
         </is>
       </c>
+      <c r="CZ32" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -8862,6 +9029,11 @@
           <t>سمك شعور</t>
         </is>
       </c>
+      <c r="CZ33" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -9099,6 +9271,11 @@
           <t>سمك هامور</t>
         </is>
       </c>
+      <c r="CZ34" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9336,6 +9513,11 @@
           <t>سمك بيات</t>
         </is>
       </c>
+      <c r="CZ35" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -9573,6 +9755,11 @@
           <t>سمك قاروص</t>
         </is>
       </c>
+      <c r="CZ36" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -9831,6 +10018,11 @@
           <t>ربيان - بحر</t>
         </is>
       </c>
+      <c r="CZ37" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -10068,6 +10260,11 @@
           <t>سمك بوري</t>
         </is>
       </c>
+      <c r="CZ38" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -10293,6 +10490,11 @@
           <t>سبيط</t>
         </is>
       </c>
+      <c r="CZ39" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -10530,6 +10732,11 @@
           <t>سمك بلطي</t>
         </is>
       </c>
+      <c r="CZ40" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -10767,6 +10974,11 @@
           <t>سمك فيلية</t>
         </is>
       </c>
+      <c r="CZ41" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -11004,6 +11216,11 @@
           <t>سمك ناجل</t>
         </is>
       </c>
+      <c r="CZ42" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -11241,6 +11458,11 @@
           <t>سمك كنعد</t>
         </is>
       </c>
+      <c r="CZ43" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -11478,6 +11700,11 @@
           <t>سمك سلمون</t>
         </is>
       </c>
+      <c r="CZ44" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -11754,6 +11981,11 @@
           <t>مياة معبأة</t>
         </is>
       </c>
+      <c r="CZ45" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -12012,6 +12244,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ46" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -12249,6 +12486,11 @@
           <t>سمك سلمون</t>
         </is>
       </c>
+      <c r="CZ47" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -12486,6 +12728,11 @@
           <t>سمك دنيس</t>
         </is>
       </c>
+      <c r="CZ48" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -12706,6 +12953,11 @@
           <t>سمك حبار</t>
         </is>
       </c>
+      <c r="CZ49" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -12943,6 +13195,11 @@
           <t>سمك كنعد</t>
         </is>
       </c>
+      <c r="CZ50" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -13180,6 +13437,11 @@
           <t>سمك سيباس</t>
         </is>
       </c>
+      <c r="CZ51" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -13417,6 +13679,11 @@
           <t>سمك عندق</t>
         </is>
       </c>
+      <c r="CZ52" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -13654,6 +13921,11 @@
           <t>سمك شعور</t>
         </is>
       </c>
+      <c r="CZ53" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -13891,6 +14163,11 @@
           <t>سمك هامور</t>
         </is>
       </c>
+      <c r="CZ54" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -14149,6 +14426,11 @@
           <t>مياة غسيل الاسماك</t>
         </is>
       </c>
+      <c r="CZ55" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -14407,6 +14689,11 @@
           <t>ربيان بحر</t>
         </is>
       </c>
+      <c r="CZ56" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -14644,6 +14931,11 @@
           <t>سمك كنعد</t>
         </is>
       </c>
+      <c r="CZ57" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -14881,6 +15173,11 @@
           <t>سمك دنيس</t>
         </is>
       </c>
+      <c r="CZ58" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -15118,6 +15415,11 @@
           <t>سمك شعور</t>
         </is>
       </c>
+      <c r="CZ59" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -15355,6 +15657,11 @@
           <t>سمك عندق</t>
         </is>
       </c>
+      <c r="CZ60" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -15592,6 +15899,11 @@
           <t>سمك هامور</t>
         </is>
       </c>
+      <c r="CZ61" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -15829,6 +16141,11 @@
           <t>سمك عروسة</t>
         </is>
       </c>
+      <c r="CZ62" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -16082,6 +16399,11 @@
           <t>ربيان مزرعة</t>
         </is>
       </c>
+      <c r="CZ63" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -16340,6 +16662,11 @@
           <t>مياه غسيل الاسماك</t>
         </is>
       </c>
+      <c r="CZ64" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -16598,6 +16925,11 @@
           <t>مياه غسيل داوات</t>
         </is>
       </c>
+      <c r="CZ65" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -16856,6 +17188,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ66" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -17114,6 +17451,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ67" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -17372,6 +17714,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ68" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -17630,6 +17977,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ69" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -17888,6 +18240,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ70" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -18146,6 +18503,11 @@
           <t>مياة غسيل حنفية</t>
         </is>
       </c>
+      <c r="CZ71" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -18404,6 +18766,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ72" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -18662,6 +19029,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ73" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الشرق</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -18896,6 +19268,11 @@
           <t>مياة حنفية للطبخ</t>
         </is>
       </c>
+      <c r="CZ74" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -19130,6 +19507,11 @@
           <t>مياة غسيل الارز و ادوات التحضير</t>
         </is>
       </c>
+      <c r="CZ75" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -19364,6 +19746,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ76" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -19598,6 +19985,11 @@
           <t>مياة حنفية</t>
         </is>
       </c>
+      <c r="CZ77" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -19832,6 +20224,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ78" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -20066,6 +20463,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ79" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -20300,6 +20702,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ80" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -20534,6 +20941,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ81" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -20768,6 +21180,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ82" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -21002,6 +21419,11 @@
           <t>مياة حنفية للطبخ</t>
         </is>
       </c>
+      <c r="CZ83" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -21236,6 +21658,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ84" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -21470,6 +21897,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ85" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -21707,6 +22139,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ86" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -21941,6 +22378,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ87" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -22175,6 +22617,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ88" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -22409,6 +22856,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ89" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -22643,6 +23095,11 @@
           <t>مياة حنفية لغسيل الادوات ١</t>
         </is>
       </c>
+      <c r="CZ90" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -22877,6 +23334,11 @@
           <t>مياة حنفية لغسيل الادوات ٢</t>
         </is>
       </c>
+      <c r="CZ91" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -23111,6 +23573,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ92" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -23345,6 +23812,11 @@
           <t>مياة حنفية لغسيل الادوات ١</t>
         </is>
       </c>
+      <c r="CZ93" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -23582,6 +24054,11 @@
           <t>مياه حنفية لغسيل الادوات ٢</t>
         </is>
       </c>
+      <c r="CZ94" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -23821,6 +24298,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ95" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -24058,6 +24540,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ96" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -24295,6 +24782,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ97" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -24532,6 +25024,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ98" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -24769,6 +25266,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ99" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -25006,6 +25508,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ100" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -25246,6 +25753,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ101" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -25483,6 +25995,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ102" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -25720,6 +26237,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ103" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -25957,6 +26479,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ104" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -26197,6 +26724,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ105" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -26437,6 +26969,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ106" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -26677,6 +27214,11 @@
           <t>مياة حنفية لغسيل الارز</t>
         </is>
       </c>
+      <c r="CZ107" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -26917,6 +27459,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ108" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -27157,6 +27704,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ109" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -27400,6 +27952,11 @@
           <t>مياه حنفية للعجانة</t>
         </is>
       </c>
+      <c r="CZ110" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -27643,6 +28200,11 @@
           <t>مياه حنفية غسيل ادوات</t>
         </is>
       </c>
+      <c r="CZ111" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -27886,6 +28448,11 @@
           <t>مياه غسيل الاسماك</t>
         </is>
       </c>
+      <c r="CZ112" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -28129,6 +28696,11 @@
           <t>ربيان مزرعة</t>
         </is>
       </c>
+      <c r="CZ113" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -28372,6 +28944,11 @@
           <t>ربيان بحري</t>
         </is>
       </c>
+      <c r="CZ114" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -28594,6 +29171,11 @@
           <t>سمك كنعد</t>
         </is>
       </c>
+      <c r="CZ115" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -28816,6 +29398,11 @@
           <t>سمك سالمون</t>
         </is>
       </c>
+      <c r="CZ116" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -29038,6 +29625,11 @@
           <t>سمك بلطي</t>
         </is>
       </c>
+      <c r="CZ117" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -29275,6 +29867,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ118" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -29512,6 +30109,11 @@
           <t>مياة حنفية لغسيل الأدوات</t>
         </is>
       </c>
+      <c r="CZ119" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -29752,6 +30354,11 @@
           <t>مياة حنفية لغسيل الأدوات(1)</t>
         </is>
       </c>
+      <c r="CZ120" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -29989,6 +30596,11 @@
           <t>مياة حنفية لغسيل الأدوات(2)</t>
         </is>
       </c>
+      <c r="CZ121" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -30235,6 +30847,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ122" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -30481,6 +31098,11 @@
           <t>مياة حنفية غسيل</t>
         </is>
       </c>
+      <c r="CZ123" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -30727,6 +31349,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ124" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -30973,6 +31600,11 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ125" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -31219,6 +31851,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ126" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -31465,6 +32102,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ127" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -31708,6 +32350,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ128" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -31951,6 +32598,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ129" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -32194,6 +32846,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ130" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -32437,6 +33094,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ131" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -32680,6 +33342,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ132" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -32923,6 +33590,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ133" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -33166,6 +33838,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ134" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -33409,6 +34086,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ135" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -33652,6 +34334,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ136" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -33895,6 +34582,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ137" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -34138,6 +34830,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ138" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -34381,6 +35078,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ139" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -34624,6 +35326,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ140" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -34867,6 +35574,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ141" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -35110,6 +35822,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ142" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -35353,6 +36070,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ143" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -35596,6 +36318,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ144" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -35839,6 +36566,11 @@
           <t>مياة حنفية</t>
         </is>
       </c>
+      <c r="CZ145" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -36082,6 +36814,11 @@
           <t>مياة حنفية لغسيل الارز</t>
         </is>
       </c>
+      <c r="CZ146" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -36325,6 +37062,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ147" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -36568,6 +37310,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ148" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -36820,6 +37567,11 @@
           <t>مياة معبأة للطبخ</t>
         </is>
       </c>
+      <c r="CZ149" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -37072,6 +37824,11 @@
           <t>مياة معبأة للعجانة</t>
         </is>
       </c>
+      <c r="CZ150" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -37315,6 +38072,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ151" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -37558,6 +38320,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ152" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -37801,6 +38568,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ153" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -38044,6 +38816,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ154" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -38287,6 +39064,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ155" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -38530,6 +39312,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ156" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -38773,6 +39560,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ157" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -39019,6 +39811,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ158" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -39265,6 +40062,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ159" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -39511,6 +40313,11 @@
           <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
+      <c r="CZ160" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -39757,6 +40564,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ161" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -40003,6 +40815,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ162" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -40249,6 +41066,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ163" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -40495,6 +41317,11 @@
           <t>مياه غسيل أدوات</t>
         </is>
       </c>
+      <c r="CZ164" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -40741,6 +41568,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ165" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -40996,6 +41828,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ166" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -41242,6 +42079,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ167" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -41488,6 +42330,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ168" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -41734,6 +42581,11 @@
           <t>مياة حنفية لغسيل الادوات - ك</t>
         </is>
       </c>
+      <c r="CZ169" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -41980,6 +42832,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ170" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -42226,6 +43083,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ171" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -42472,6 +43334,11 @@
           <t>مياة حنفية للطبخ م.ك</t>
         </is>
       </c>
+      <c r="CZ172" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -42718,6 +43585,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ173" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -42964,6 +43836,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ174" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -43210,6 +44087,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ175" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -43456,6 +44338,11 @@
           <t>A مياة</t>
         </is>
       </c>
+      <c r="DA176" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -43702,6 +44589,11 @@
           <t>B مياة</t>
         </is>
       </c>
+      <c r="DA177" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -43948,6 +44840,11 @@
           <t>C مياة</t>
         </is>
       </c>
+      <c r="DA178" t="inlineStr">
+        <is>
+          <t>private</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -44194,6 +45091,11 @@
           <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
+      <c r="CZ179" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -44440,6 +45342,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ180" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -44686,6 +45593,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ181" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -44941,6 +45853,11 @@
           <t>مياة معبأة للطبخ م.ك</t>
         </is>
       </c>
+      <c r="CZ182" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -45187,6 +46104,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ183" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -45433,6 +46355,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ184" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -45679,6 +46606,11 @@
           <t>موية غسيل ادوات</t>
         </is>
       </c>
+      <c r="CZ185" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -45925,6 +46857,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ186" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -46171,6 +47108,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ187" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -46417,6 +47359,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ188" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -46663,6 +47610,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ189" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -46909,6 +47861,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ190" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -47158,6 +48115,11 @@
           <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
+      <c r="CZ191" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -47407,6 +48369,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ192" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -47656,6 +48623,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ193" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -47905,6 +48877,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ194" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -48154,6 +49131,11 @@
           <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
+      <c r="CZ195" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -48403,6 +49385,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ196" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -48652,6 +49639,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ197" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -48901,6 +49893,11 @@
           <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
+      <c r="CZ198" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -49150,6 +50147,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ199" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -49399,6 +50401,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ200" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -49648,6 +50655,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ201" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -49897,6 +50909,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ202" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -50146,6 +51163,11 @@
           <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
+      <c r="CZ203" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -50395,6 +51417,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ204" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -50638,6 +51665,11 @@
           <t>مياة حنفية للغسيل م.ك</t>
         </is>
       </c>
+      <c r="CZ205" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -50884,6 +51916,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ206" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -51130,6 +52167,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ207" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -51381,6 +52423,11 @@
           <t>مياة حنفية م.ك</t>
         </is>
       </c>
+      <c r="CZ208" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -51627,6 +52674,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ209" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -51873,6 +52925,11 @@
           <t>مياة حنفية لغسيل الاسماك م.ك</t>
         </is>
       </c>
+      <c r="CZ210" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -52119,6 +53176,11 @@
           <t>مياة حنفية لغسيل الادوات م.ك</t>
         </is>
       </c>
+      <c r="CZ211" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -52365,6 +53427,11 @@
           <t>مياةحنفية للغسيل م.ك</t>
         </is>
       </c>
+      <c r="CZ212" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -52590,6 +53657,11 @@
           <t>سمك دنيس ني م.ك</t>
         </is>
       </c>
+      <c r="CZ213" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -52815,6 +53887,11 @@
           <t>سمك سلمون ني م.ك</t>
         </is>
       </c>
+      <c r="CZ214" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -53040,6 +54117,11 @@
           <t>سمك كنعد ني م.ك</t>
         </is>
       </c>
+      <c r="CZ215" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -53281,6 +54363,11 @@
           <t>مياة حنفية لغسيل الادوات</t>
         </is>
       </c>
+      <c r="CZ216" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -53531,6 +54618,11 @@
           <t>مياه معاباة للطبخ</t>
         </is>
       </c>
+      <c r="CZ217" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -53772,6 +54864,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ218" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -54013,6 +55110,11 @@
           <t>مياه فلتر</t>
         </is>
       </c>
+      <c r="CZ219" t="inlineStr">
+        <is>
+          <t>فرع أمانة في المنطقة الوسطى</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -54246,6 +55348,11 @@
           <t>مياه حنفيه لغسيل الارز</t>
         </is>
       </c>
+      <c r="DA220" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -54479,9 +55586,14 @@
           <t>مياه حنفيه لغسيل الادوات</t>
         </is>
       </c>
+      <c r="DA221" t="inlineStr">
+        <is>
+          <t>no_municipality</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CZ221"/>
+  <autoFilter ref="A1:DB221"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -54492,7 +55604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D109"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -54518,7 +55630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Columns: 104</t>
+          <t>Columns: 106</t>
         </is>
       </c>
     </row>
@@ -56333,16 +57445,52 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>sector</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>215</v>
+      </c>
+      <c r="C109" t="n">
+        <v>5</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>فرع أمانة في الغرب | فرع أمانة في الغرب | فرع أمانة في الغرب</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>sector_flag</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" t="n">
+        <v>215</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>private | private | private</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>sample_code</t>
         </is>
       </c>
-      <c r="B109" t="n">
-        <v>0</v>
-      </c>
-      <c r="C109" t="n">
+      <c r="B111" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" t="n">
         <v>220</v>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/clean/chemistry/chem_heavy_metals_2024.xlsx
+++ b/clean/chemistry/chem_heavy_metals_2024.xlsx
@@ -5762,12 +5762,7 @@
       </c>
       <c r="CW20" t="inlineStr">
         <is>
-          <t>أغذية متنوعة</t>
-        </is>
-      </c>
-      <c r="CX20" t="inlineStr">
-        <is>
-          <t>defaulted</t>
+          <t>الأسماك والمأكولات البحرية</t>
         </is>
       </c>
       <c r="CY20" t="inlineStr">
@@ -5992,12 +5987,7 @@
       </c>
       <c r="CW21" t="inlineStr">
         <is>
-          <t>أغذية متنوعة</t>
-        </is>
-      </c>
-      <c r="CX21" t="inlineStr">
-        <is>
-          <t>defaulted</t>
+          <t>الأسماك والمأكولات البحرية</t>
         </is>
       </c>
       <c r="CY21" t="inlineStr">
@@ -7264,7 +7254,7 @@
       </c>
       <c r="CW26" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
@@ -8774,12 +8764,7 @@
       </c>
       <c r="CW32" t="inlineStr">
         <is>
-          <t>أغذية متنوعة</t>
-        </is>
-      </c>
-      <c r="CX32" t="inlineStr">
-        <is>
-          <t>defaulted</t>
+          <t>الأسماك والمأكولات البحرية</t>
         </is>
       </c>
       <c r="CY32" t="inlineStr">
@@ -10005,12 +9990,7 @@
       </c>
       <c r="CW37" t="inlineStr">
         <is>
-          <t>أغذية متنوعة</t>
-        </is>
-      </c>
-      <c r="CX37" t="inlineStr">
-        <is>
-          <t>defaulted</t>
+          <t>الأسماك والمأكولات البحرية</t>
         </is>
       </c>
       <c r="CY37" t="inlineStr">
@@ -10477,12 +10457,7 @@
       </c>
       <c r="CW39" t="inlineStr">
         <is>
-          <t>أغذية متنوعة</t>
-        </is>
-      </c>
-      <c r="CX39" t="inlineStr">
-        <is>
-          <t>defaulted</t>
+          <t>الأسماك والمأكولات البحرية</t>
         </is>
       </c>
       <c r="CY39" t="inlineStr">
@@ -11973,7 +11948,7 @@
       </c>
       <c r="CW45" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="CY45" t="inlineStr">
@@ -14676,12 +14651,7 @@
       </c>
       <c r="CW56" t="inlineStr">
         <is>
-          <t>أغذية متنوعة</t>
-        </is>
-      </c>
-      <c r="CX56" t="inlineStr">
-        <is>
-          <t>defaulted</t>
+          <t>الأسماك والمأكولات البحرية</t>
         </is>
       </c>
       <c r="CY56" t="inlineStr">
@@ -16386,12 +16356,7 @@
       </c>
       <c r="CW63" t="inlineStr">
         <is>
-          <t>أغذية متنوعة</t>
-        </is>
-      </c>
-      <c r="CX63" t="inlineStr">
-        <is>
-          <t>defaulted</t>
+          <t>الأسماك والمأكولات البحرية</t>
         </is>
       </c>
       <c r="CY63" t="inlineStr">
@@ -37559,7 +37524,7 @@
       </c>
       <c r="CW149" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="CY149" t="inlineStr">
@@ -37816,7 +37781,7 @@
       </c>
       <c r="CW150" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="CY150" t="inlineStr">
@@ -45845,7 +45810,7 @@
       </c>
       <c r="CW182" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="CY182" t="inlineStr">
@@ -57413,14 +57378,14 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C107" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>defaulted | defaulted | defaulted</t>
+          <t>defaulted | defaulted</t>
         </is>
       </c>
     </row>

--- a/clean/chemistry/chem_heavy_metals_2024.xlsx
+++ b/clean/chemistry/chem_heavy_metals_2024.xlsx
@@ -28648,12 +28648,7 @@
       </c>
       <c r="CW113" t="inlineStr">
         <is>
-          <t>أغذية متنوعة</t>
-        </is>
-      </c>
-      <c r="CX113" t="inlineStr">
-        <is>
-          <t>defaulted</t>
+          <t>الأسماك والمأكولات البحرية</t>
         </is>
       </c>
       <c r="CY113" t="inlineStr">
@@ -28896,12 +28891,7 @@
       </c>
       <c r="CW114" t="inlineStr">
         <is>
-          <t>أغذية متنوعة</t>
-        </is>
-      </c>
-      <c r="CX114" t="inlineStr">
-        <is>
-          <t>defaulted</t>
+          <t>الأسماك والمأكولات البحرية</t>
         </is>
       </c>
       <c r="CY114" t="inlineStr">
@@ -41785,7 +41775,7 @@
       </c>
       <c r="CW166" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="CY166" t="inlineStr">
@@ -54575,7 +54565,7 @@
       </c>
       <c r="CW217" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه شرب/معبأة</t>
         </is>
       </c>
       <c r="CY217" t="inlineStr">
@@ -57378,16 +57368,12 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C107" t="n">
-        <v>218</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>defaulted | defaulted</t>
-        </is>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="D107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">

--- a/clean/chemistry/chem_heavy_metals_2024.xlsx
+++ b/clean/chemistry/chem_heavy_metals_2024.xlsx
@@ -3527,7 +3527,7 @@
       </c>
       <c r="CW11" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
@@ -4053,7 +4053,7 @@
       </c>
       <c r="CW13" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY13" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="CW25" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY25" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="CW26" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY26" t="inlineStr">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="CW27" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY27" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="CW28" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY28" t="inlineStr">
@@ -11948,7 +11948,7 @@
       </c>
       <c r="CW45" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY45" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="CW46" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY46" t="inlineStr">
@@ -14393,7 +14393,7 @@
       </c>
       <c r="CW55" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY55" t="inlineStr">
@@ -16619,7 +16619,7 @@
       </c>
       <c r="CW64" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY64" t="inlineStr">
@@ -16882,7 +16882,7 @@
       </c>
       <c r="CW65" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY65" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="CW66" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY66" t="inlineStr">
@@ -17408,7 +17408,7 @@
       </c>
       <c r="CW67" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY67" t="inlineStr">
@@ -17671,7 +17671,7 @@
       </c>
       <c r="CW68" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY68" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="CW69" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY69" t="inlineStr">
@@ -18197,7 +18197,7 @@
       </c>
       <c r="CW70" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY70" t="inlineStr">
@@ -18460,7 +18460,7 @@
       </c>
       <c r="CW71" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY71" t="inlineStr">
@@ -18723,7 +18723,7 @@
       </c>
       <c r="CW72" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY72" t="inlineStr">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="CW73" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY73" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="CW74" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY74" t="inlineStr">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="CW75" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY75" t="inlineStr">
@@ -19703,7 +19703,7 @@
       </c>
       <c r="CW76" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY76" t="inlineStr">
@@ -19942,7 +19942,7 @@
       </c>
       <c r="CW77" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY77" t="inlineStr">
@@ -20181,7 +20181,7 @@
       </c>
       <c r="CW78" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY78" t="inlineStr">
@@ -20420,7 +20420,7 @@
       </c>
       <c r="CW79" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY79" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="CW80" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY80" t="inlineStr">
@@ -20898,7 +20898,7 @@
       </c>
       <c r="CW81" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY81" t="inlineStr">
@@ -21137,7 +21137,7 @@
       </c>
       <c r="CW82" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY82" t="inlineStr">
@@ -21376,7 +21376,7 @@
       </c>
       <c r="CW83" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY83" t="inlineStr">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="CW84" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY84" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="CW85" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY85" t="inlineStr">
@@ -22096,7 +22096,7 @@
       </c>
       <c r="CW86" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY86" t="inlineStr">
@@ -22335,7 +22335,7 @@
       </c>
       <c r="CW87" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY87" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="CW88" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY88" t="inlineStr">
@@ -22813,7 +22813,7 @@
       </c>
       <c r="CW89" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY89" t="inlineStr">
@@ -23052,7 +23052,7 @@
       </c>
       <c r="CW90" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY90" t="inlineStr">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="CW91" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY91" t="inlineStr">
@@ -23530,7 +23530,7 @@
       </c>
       <c r="CW92" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY92" t="inlineStr">
@@ -23769,7 +23769,7 @@
       </c>
       <c r="CW93" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY93" t="inlineStr">
@@ -24011,7 +24011,7 @@
       </c>
       <c r="CW94" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY94" t="inlineStr">
@@ -24255,7 +24255,7 @@
       </c>
       <c r="CW95" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY95" t="inlineStr">
@@ -24497,7 +24497,7 @@
       </c>
       <c r="CW96" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY96" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="CW97" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY97" t="inlineStr">
@@ -24981,7 +24981,7 @@
       </c>
       <c r="CW98" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY98" t="inlineStr">
@@ -25223,7 +25223,7 @@
       </c>
       <c r="CW99" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY99" t="inlineStr">
@@ -25465,7 +25465,7 @@
       </c>
       <c r="CW100" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY100" t="inlineStr">
@@ -25710,7 +25710,7 @@
       </c>
       <c r="CW101" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY101" t="inlineStr">
@@ -25952,7 +25952,7 @@
       </c>
       <c r="CW102" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY102" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="CW103" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY103" t="inlineStr">
@@ -26436,7 +26436,7 @@
       </c>
       <c r="CW104" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY104" t="inlineStr">
@@ -26681,7 +26681,7 @@
       </c>
       <c r="CW105" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY105" t="inlineStr">
@@ -26926,7 +26926,7 @@
       </c>
       <c r="CW106" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY106" t="inlineStr">
@@ -27171,7 +27171,7 @@
       </c>
       <c r="CW107" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY107" t="inlineStr">
@@ -27416,7 +27416,7 @@
       </c>
       <c r="CW108" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY108" t="inlineStr">
@@ -27661,7 +27661,7 @@
       </c>
       <c r="CW109" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY109" t="inlineStr">
@@ -27909,7 +27909,7 @@
       </c>
       <c r="CW110" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY110" t="inlineStr">
@@ -28157,7 +28157,7 @@
       </c>
       <c r="CW111" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY111" t="inlineStr">
@@ -28405,7 +28405,7 @@
       </c>
       <c r="CW112" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY112" t="inlineStr">
@@ -29814,7 +29814,7 @@
       </c>
       <c r="CW118" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY118" t="inlineStr">
@@ -30056,7 +30056,7 @@
       </c>
       <c r="CW119" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY119" t="inlineStr">
@@ -30301,7 +30301,7 @@
       </c>
       <c r="CW120" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY120" t="inlineStr">
@@ -30543,7 +30543,7 @@
       </c>
       <c r="CW121" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY121" t="inlineStr">
@@ -30794,7 +30794,7 @@
       </c>
       <c r="CW122" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY122" t="inlineStr">
@@ -31045,7 +31045,7 @@
       </c>
       <c r="CW123" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY123" t="inlineStr">
@@ -31296,7 +31296,7 @@
       </c>
       <c r="CW124" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY124" t="inlineStr">
@@ -31547,7 +31547,7 @@
       </c>
       <c r="CW125" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY125" t="inlineStr">
@@ -31798,7 +31798,7 @@
       </c>
       <c r="CW126" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY126" t="inlineStr">
@@ -32049,7 +32049,7 @@
       </c>
       <c r="CW127" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY127" t="inlineStr">
@@ -32297,7 +32297,7 @@
       </c>
       <c r="CW128" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY128" t="inlineStr">
@@ -32545,7 +32545,7 @@
       </c>
       <c r="CW129" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY129" t="inlineStr">
@@ -32793,7 +32793,7 @@
       </c>
       <c r="CW130" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY130" t="inlineStr">
@@ -33041,7 +33041,7 @@
       </c>
       <c r="CW131" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY131" t="inlineStr">
@@ -33289,7 +33289,7 @@
       </c>
       <c r="CW132" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY132" t="inlineStr">
@@ -33537,7 +33537,7 @@
       </c>
       <c r="CW133" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY133" t="inlineStr">
@@ -33785,7 +33785,7 @@
       </c>
       <c r="CW134" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY134" t="inlineStr">
@@ -34033,7 +34033,7 @@
       </c>
       <c r="CW135" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY135" t="inlineStr">
@@ -34281,7 +34281,7 @@
       </c>
       <c r="CW136" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY136" t="inlineStr">
@@ -34529,7 +34529,7 @@
       </c>
       <c r="CW137" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY137" t="inlineStr">
@@ -34777,7 +34777,7 @@
       </c>
       <c r="CW138" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY138" t="inlineStr">
@@ -35025,7 +35025,7 @@
       </c>
       <c r="CW139" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY139" t="inlineStr">
@@ -35273,7 +35273,7 @@
       </c>
       <c r="CW140" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY140" t="inlineStr">
@@ -35521,7 +35521,7 @@
       </c>
       <c r="CW141" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY141" t="inlineStr">
@@ -35769,7 +35769,7 @@
       </c>
       <c r="CW142" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY142" t="inlineStr">
@@ -36017,7 +36017,7 @@
       </c>
       <c r="CW143" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY143" t="inlineStr">
@@ -36265,7 +36265,7 @@
       </c>
       <c r="CW144" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY144" t="inlineStr">
@@ -36513,7 +36513,7 @@
       </c>
       <c r="CW145" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY145" t="inlineStr">
@@ -36761,7 +36761,7 @@
       </c>
       <c r="CW146" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY146" t="inlineStr">
@@ -37009,7 +37009,7 @@
       </c>
       <c r="CW147" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY147" t="inlineStr">
@@ -37257,7 +37257,7 @@
       </c>
       <c r="CW148" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY148" t="inlineStr">
@@ -37514,7 +37514,7 @@
       </c>
       <c r="CW149" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY149" t="inlineStr">
@@ -37771,7 +37771,7 @@
       </c>
       <c r="CW150" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY150" t="inlineStr">
@@ -38019,7 +38019,7 @@
       </c>
       <c r="CW151" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY151" t="inlineStr">
@@ -38267,7 +38267,7 @@
       </c>
       <c r="CW152" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY152" t="inlineStr">
@@ -38515,7 +38515,7 @@
       </c>
       <c r="CW153" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY153" t="inlineStr">
@@ -38763,7 +38763,7 @@
       </c>
       <c r="CW154" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY154" t="inlineStr">
@@ -39011,7 +39011,7 @@
       </c>
       <c r="CW155" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY155" t="inlineStr">
@@ -39259,7 +39259,7 @@
       </c>
       <c r="CW156" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY156" t="inlineStr">
@@ -39507,7 +39507,7 @@
       </c>
       <c r="CW157" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY157" t="inlineStr">
@@ -39758,7 +39758,7 @@
       </c>
       <c r="CW158" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY158" t="inlineStr">
@@ -40009,7 +40009,7 @@
       </c>
       <c r="CW159" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY159" t="inlineStr">
@@ -40260,7 +40260,7 @@
       </c>
       <c r="CW160" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY160" t="inlineStr">
@@ -40511,7 +40511,7 @@
       </c>
       <c r="CW161" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY161" t="inlineStr">
@@ -40762,7 +40762,7 @@
       </c>
       <c r="CW162" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY162" t="inlineStr">
@@ -41013,7 +41013,7 @@
       </c>
       <c r="CW163" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY163" t="inlineStr">
@@ -41264,7 +41264,7 @@
       </c>
       <c r="CW164" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY164" t="inlineStr">
@@ -41515,7 +41515,7 @@
       </c>
       <c r="CW165" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY165" t="inlineStr">
@@ -41775,7 +41775,7 @@
       </c>
       <c r="CW166" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY166" t="inlineStr">
@@ -42026,7 +42026,7 @@
       </c>
       <c r="CW167" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY167" t="inlineStr">
@@ -42277,7 +42277,7 @@
       </c>
       <c r="CW168" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY168" t="inlineStr">
@@ -42528,7 +42528,7 @@
       </c>
       <c r="CW169" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY169" t="inlineStr">
@@ -42779,7 +42779,7 @@
       </c>
       <c r="CW170" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY170" t="inlineStr">
@@ -43030,7 +43030,7 @@
       </c>
       <c r="CW171" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY171" t="inlineStr">
@@ -43281,7 +43281,7 @@
       </c>
       <c r="CW172" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY172" t="inlineStr">
@@ -43532,7 +43532,7 @@
       </c>
       <c r="CW173" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY173" t="inlineStr">
@@ -43783,7 +43783,7 @@
       </c>
       <c r="CW174" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY174" t="inlineStr">
@@ -44034,7 +44034,7 @@
       </c>
       <c r="CW175" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY175" t="inlineStr">
@@ -44285,7 +44285,7 @@
       </c>
       <c r="CW176" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY176" t="inlineStr">
@@ -44536,7 +44536,7 @@
       </c>
       <c r="CW177" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY177" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="CW178" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY178" t="inlineStr">
@@ -45038,7 +45038,7 @@
       </c>
       <c r="CW179" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY179" t="inlineStr">
@@ -45289,7 +45289,7 @@
       </c>
       <c r="CW180" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY180" t="inlineStr">
@@ -45540,7 +45540,7 @@
       </c>
       <c r="CW181" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY181" t="inlineStr">
@@ -45800,7 +45800,7 @@
       </c>
       <c r="CW182" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY182" t="inlineStr">
@@ -46051,7 +46051,7 @@
       </c>
       <c r="CW183" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY183" t="inlineStr">
@@ -46302,7 +46302,7 @@
       </c>
       <c r="CW184" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY184" t="inlineStr">
@@ -46553,7 +46553,7 @@
       </c>
       <c r="CW185" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY185" t="inlineStr">
@@ -46804,7 +46804,7 @@
       </c>
       <c r="CW186" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY186" t="inlineStr">
@@ -47055,7 +47055,7 @@
       </c>
       <c r="CW187" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY187" t="inlineStr">
@@ -47306,7 +47306,7 @@
       </c>
       <c r="CW188" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY188" t="inlineStr">
@@ -47557,7 +47557,7 @@
       </c>
       <c r="CW189" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY189" t="inlineStr">
@@ -47808,7 +47808,7 @@
       </c>
       <c r="CW190" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY190" t="inlineStr">
@@ -48062,7 +48062,7 @@
       </c>
       <c r="CW191" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY191" t="inlineStr">
@@ -48316,7 +48316,7 @@
       </c>
       <c r="CW192" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY192" t="inlineStr">
@@ -48570,7 +48570,7 @@
       </c>
       <c r="CW193" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY193" t="inlineStr">
@@ -48824,7 +48824,7 @@
       </c>
       <c r="CW194" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY194" t="inlineStr">
@@ -49078,7 +49078,7 @@
       </c>
       <c r="CW195" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY195" t="inlineStr">
@@ -49332,7 +49332,7 @@
       </c>
       <c r="CW196" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY196" t="inlineStr">
@@ -49586,7 +49586,7 @@
       </c>
       <c r="CW197" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY197" t="inlineStr">
@@ -49840,7 +49840,7 @@
       </c>
       <c r="CW198" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY198" t="inlineStr">
@@ -50094,7 +50094,7 @@
       </c>
       <c r="CW199" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY199" t="inlineStr">
@@ -50348,7 +50348,7 @@
       </c>
       <c r="CW200" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY200" t="inlineStr">
@@ -50602,7 +50602,7 @@
       </c>
       <c r="CW201" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY201" t="inlineStr">
@@ -50856,7 +50856,7 @@
       </c>
       <c r="CW202" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY202" t="inlineStr">
@@ -51110,7 +51110,7 @@
       </c>
       <c r="CW203" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY203" t="inlineStr">
@@ -51364,7 +51364,7 @@
       </c>
       <c r="CW204" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY204" t="inlineStr">
@@ -51612,7 +51612,7 @@
       </c>
       <c r="CW205" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY205" t="inlineStr">
@@ -51863,7 +51863,7 @@
       </c>
       <c r="CW206" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY206" t="inlineStr">
@@ -52114,7 +52114,7 @@
       </c>
       <c r="CW207" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY207" t="inlineStr">
@@ -52370,7 +52370,7 @@
       </c>
       <c r="CW208" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY208" t="inlineStr">
@@ -52621,7 +52621,7 @@
       </c>
       <c r="CW209" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY209" t="inlineStr">
@@ -52872,7 +52872,7 @@
       </c>
       <c r="CW210" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY210" t="inlineStr">
@@ -53123,7 +53123,7 @@
       </c>
       <c r="CW211" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY211" t="inlineStr">
@@ -53374,7 +53374,7 @@
       </c>
       <c r="CW212" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY212" t="inlineStr">
@@ -54310,7 +54310,7 @@
       </c>
       <c r="CW216" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY216" t="inlineStr">
@@ -54565,7 +54565,7 @@
       </c>
       <c r="CW217" t="inlineStr">
         <is>
-          <t>مياه شرب/معبأة</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY217" t="inlineStr">
@@ -54811,7 +54811,7 @@
       </c>
       <c r="CW218" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY218" t="inlineStr">
@@ -55057,7 +55057,7 @@
       </c>
       <c r="CW219" t="inlineStr">
         <is>
-          <t>مياه فلتر</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY219" t="inlineStr">
@@ -55295,7 +55295,7 @@
       </c>
       <c r="CW220" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY220" t="inlineStr">
@@ -55533,7 +55533,7 @@
       </c>
       <c r="CW221" t="inlineStr">
         <is>
-          <t>مياه الحنفية</t>
+          <t>مياه صالحة للشرب</t>
         </is>
       </c>
       <c r="CY221" t="inlineStr">
